--- a/Gantt Chart Cronograma.xlsx
+++ b/Gantt Chart Cronograma.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rayke\Documents\Programacion Web\Programacion 3\Proyecto Final\Reto-3-Grupo-J\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DACDE27-407F-427D-960B-F96089BC8E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2B6B4C-5712-4887-B945-2AAA1E2D2CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="7650" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="Display_Week">'Project Schedule'!$Q$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Project Schedule'!$5:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Project Schedule'!$6:$8</definedName>
     <definedName name="Project_Start">'Project Schedule'!$Q$1</definedName>
     <definedName name="task_end" localSheetId="0">'Project Schedule'!$F1</definedName>
     <definedName name="task_progress" localSheetId="0">'Project Schedule'!$D1</definedName>
@@ -44,8 +44,90 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Raykel Villar</author>
+  </authors>
+  <commentList>
+    <comment ref="B33" authorId="0" shapeId="0" xr:uid="{CB5F8FE0-3A07-4DD7-9A6A-C9EB65374E0F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Raykel Villar:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Modificar Productos, Agregar nuevos, deshabilitar productos. Cambiar Roles.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0" shapeId="0" xr:uid="{A3221A40-20FC-434F-8F6B-632DA2F27663}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Raykel Villar:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Modificar Productos, Agregar nuevos, deshabilitar productos. Cambiar Roles.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0" shapeId="0" xr:uid="{AB31A21F-8F32-4341-99B6-39E3A43DB709}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Raykel Villar:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Modificar Productos, Agregar nuevos, deshabilitar productos. Cambiar Roles.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
   <si>
     <t xml:space="preserve">Do not delete this row. This row is hidden to preserve a formula that is used to highlight the current day within the project schedule. </t>
   </si>
@@ -87,6 +169,87 @@
   </si>
   <si>
     <t>Raykel Villar</t>
+  </si>
+  <si>
+    <t>Chery Viola</t>
+  </si>
+  <si>
+    <t>Alfredo Feliz</t>
+  </si>
+  <si>
+    <t>Creacion Repositorio Git-Hub</t>
+  </si>
+  <si>
+    <t>Creacion de Diagrama De Gantt</t>
+  </si>
+  <si>
+    <t>Visita al Negocio</t>
+  </si>
+  <si>
+    <t>Todos</t>
+  </si>
+  <si>
+    <t>A. Acta de Inicio del Proyecto (Project Charter)</t>
+  </si>
+  <si>
+    <t>B. Estructura de Desglose del Trabajo (EDT / WBS)</t>
+  </si>
+  <si>
+    <t>Reunion Virtual Google Meets</t>
+  </si>
+  <si>
+    <t>Paginas Login y Registro HTML</t>
+  </si>
+  <si>
+    <t>Paginas Login y Registro CSS</t>
+  </si>
+  <si>
+    <t>Paginas Login y Registro Backend</t>
+  </si>
+  <si>
+    <t>Crear Roles Backend</t>
+  </si>
+  <si>
+    <t>Base Datos</t>
+  </si>
+  <si>
+    <t>Pagina De Inicio HTML</t>
+  </si>
+  <si>
+    <t>Pagina De Inicio CSS</t>
+  </si>
+  <si>
+    <t>Pagina De Inicio Backend</t>
+  </si>
+  <si>
+    <t>Pagina De Departamentos HTML</t>
+  </si>
+  <si>
+    <t>Pagina De Departamentos CSS</t>
+  </si>
+  <si>
+    <t>Pagina De Departamentos Backend</t>
+  </si>
+  <si>
+    <t>Pagina Lista de Favoritos HTML</t>
+  </si>
+  <si>
+    <t>Pagina Lista de Favoritos CSS</t>
+  </si>
+  <si>
+    <t>Pagina Lista de Favoritos Backend</t>
+  </si>
+  <si>
+    <t>Pagina Administrador HTML</t>
+  </si>
+  <si>
+    <t>Pagina Administrador CSS</t>
+  </si>
+  <si>
+    <t>Pagina Administrador Backend</t>
+  </si>
+  <si>
+    <t>Crear React App</t>
   </si>
 </sst>
 </file>
@@ -100,7 +263,7 @@
     <numFmt numFmtId="166" formatCode="mmm\ d\,\ yyyy"/>
     <numFmt numFmtId="167" formatCode="d"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,13 +354,6 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -308,6 +464,19 @@
       <name val="Arial Black"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -617,7 +786,7 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -654,9 +823,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="8">
       <alignment horizontal="right" indent="1"/>
@@ -670,38 +836,38 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -713,73 +879,67 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="1" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="1" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="7" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="7" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -788,28 +948,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="5" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="8" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="8" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
       <extLst>
@@ -818,47 +975,105 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -1301,6 +1516,10 @@
 </FeaturePropertyBags>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1503,29 +1722,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD29"/>
+  <dimension ref="A1:AD46"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="44.33203125" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="10.6640625" customWidth="1"/>
     <col min="7" max="7" width="2.6640625" customWidth="1"/>
     <col min="8" max="8" width="6" hidden="1" customWidth="1"/>
-    <col min="9" max="14" width="2.6640625" customWidth="1"/>
-    <col min="15" max="15" width="4.75" customWidth="1"/>
-    <col min="16" max="29" width="2.6640625" customWidth="1"/>
+    <col min="9" max="29" width="4.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="90" customHeight="1" x14ac:dyDescent="1.7">
       <c r="A1" s="7"/>
-      <c r="B1" s="70" t="s">
+      <c r="B1" s="66" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="11"/>
@@ -1533,1090 +1750,1686 @@
       <c r="E1" s="13"/>
       <c r="F1" s="14"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="81" t="s">
+      <c r="I1" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
       <c r="P1" s="17"/>
-      <c r="Q1" s="79">
+      <c r="Q1" s="75">
         <v>46130</v>
       </c>
-      <c r="R1" s="80"/>
-      <c r="S1" s="80"/>
-      <c r="T1" s="80"/>
-      <c r="U1" s="80"/>
-      <c r="V1" s="80"/>
-      <c r="W1" s="80"/>
-      <c r="X1" s="80"/>
-      <c r="Y1" s="80"/>
-      <c r="Z1" s="80"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
+      <c r="W1" s="76"/>
+      <c r="X1" s="76"/>
+      <c r="Y1" s="76"/>
+      <c r="Z1" s="76"/>
     </row>
     <row r="2" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="69"/>
+      <c r="C2" s="65"/>
       <c r="D2" s="15"/>
       <c r="E2" s="16"/>
       <c r="F2" s="15"/>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="77">
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="83">
         <v>2</v>
       </c>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="78"/>
-      <c r="U2" s="78"/>
-      <c r="V2" s="78"/>
-      <c r="W2" s="78"/>
-      <c r="X2" s="78"/>
-      <c r="Y2" s="78"/>
-      <c r="Z2" s="78"/>
-    </row>
-    <row r="3" spans="1:30" s="19" customFormat="1" ht="44.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R2" s="84"/>
+      <c r="S2" s="84"/>
+      <c r="T2" s="84"/>
+      <c r="U2" s="84"/>
+      <c r="V2" s="84"/>
+      <c r="W2" s="84"/>
+      <c r="X2" s="84"/>
+      <c r="Y2" s="84"/>
+      <c r="Z2" s="84"/>
+    </row>
+    <row r="3" spans="1:30" s="18" customFormat="1" ht="44.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="18"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21"/>
-      <c r="I3" s="81" t="s">
+      <c r="B3" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="19"/>
+      <c r="E3" s="20"/>
+      <c r="I3" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
-      <c r="O3" s="82"/>
-      <c r="Q3" s="79">
+      <c r="J3" s="78"/>
+      <c r="K3" s="78"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="Q3" s="75">
         <v>46150</v>
       </c>
-      <c r="R3" s="80"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="80"/>
-      <c r="V3" s="80"/>
-      <c r="W3" s="80"/>
-      <c r="X3" s="80"/>
-      <c r="Y3" s="80"/>
-      <c r="Z3" s="80"/>
-    </row>
-    <row r="4" spans="1:30" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="W3" s="76"/>
+      <c r="X3" s="76"/>
+      <c r="Y3" s="76"/>
+      <c r="Z3" s="76"/>
+    </row>
+    <row r="4" spans="1:30" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
-      <c r="B4" s="18"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="21"/>
-    </row>
-    <row r="5" spans="1:30" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="22"/>
-      <c r="E5" s="23"/>
-      <c r="I5" s="73">
-        <f>I6</f>
+      <c r="B4" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:30" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="19"/>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:30" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="21"/>
+      <c r="E6" s="22"/>
+      <c r="I6" s="81">
+        <f>I7</f>
         <v>46130</v>
       </c>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74">
-        <f>P6</f>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="82"/>
+      <c r="N6" s="82"/>
+      <c r="O6" s="82"/>
+      <c r="P6" s="82">
+        <f>P7</f>
         <v>46137</v>
       </c>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
-      <c r="W5" s="74">
-        <f>W6</f>
+      <c r="Q6" s="82"/>
+      <c r="R6" s="82"/>
+      <c r="S6" s="82"/>
+      <c r="T6" s="82"/>
+      <c r="U6" s="82"/>
+      <c r="V6" s="82"/>
+      <c r="W6" s="82">
+        <f>W7</f>
         <v>46144</v>
       </c>
-      <c r="X5" s="74"/>
-      <c r="Y5" s="74"/>
-      <c r="Z5" s="74"/>
-      <c r="AA5" s="74"/>
-      <c r="AB5" s="74"/>
-      <c r="AC5" s="74"/>
-    </row>
-    <row r="6" spans="1:30" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="85"/>
-      <c r="B6" s="86" t="s">
+      <c r="X6" s="82"/>
+      <c r="Y6" s="82"/>
+      <c r="Z6" s="82"/>
+      <c r="AA6" s="82"/>
+      <c r="AB6" s="82"/>
+      <c r="AC6" s="82"/>
+    </row>
+    <row r="7" spans="1:30" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="69"/>
+      <c r="B7" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="88" t="s">
+      <c r="C7" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D7" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="75" t="s">
+      <c r="E7" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="75" t="s">
+      <c r="F7" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I7" s="23">
         <f>Project_Start-WEEKDAY(Project_Start,16)*(Display_Week-1)+1</f>
         <v>46130</v>
       </c>
-      <c r="J6" s="24">
-        <f>I6+1</f>
+      <c r="J7" s="23">
+        <f>I7+1</f>
         <v>46131</v>
       </c>
-      <c r="K6" s="24">
-        <f t="shared" ref="K6:AC6" si="0">J6+1</f>
+      <c r="K7" s="23">
+        <f t="shared" ref="K7:AC7" si="0">J7+1</f>
         <v>46132</v>
       </c>
-      <c r="L6" s="24">
+      <c r="L7" s="23">
         <f t="shared" si="0"/>
         <v>46133</v>
       </c>
-      <c r="M6" s="24">
+      <c r="M7" s="23">
         <f t="shared" si="0"/>
         <v>46134</v>
       </c>
-      <c r="N6" s="24">
+      <c r="N7" s="23">
         <f t="shared" si="0"/>
         <v>46135</v>
       </c>
-      <c r="O6" s="25">
+      <c r="O7" s="24">
         <f t="shared" si="0"/>
         <v>46136</v>
       </c>
-      <c r="P6" s="26">
-        <f>O6+1</f>
+      <c r="P7" s="25">
+        <f>O7+1</f>
         <v>46137</v>
       </c>
-      <c r="Q6" s="24">
-        <f>P6+1</f>
+      <c r="Q7" s="23">
+        <f>P7+1</f>
         <v>46138</v>
       </c>
-      <c r="R6" s="24">
+      <c r="R7" s="23">
         <f t="shared" si="0"/>
         <v>46139</v>
       </c>
-      <c r="S6" s="24">
+      <c r="S7" s="23">
         <f t="shared" si="0"/>
         <v>46140</v>
       </c>
-      <c r="T6" s="24">
+      <c r="T7" s="23">
         <f t="shared" si="0"/>
         <v>46141</v>
       </c>
-      <c r="U6" s="24">
+      <c r="U7" s="23">
         <f t="shared" si="0"/>
         <v>46142</v>
       </c>
-      <c r="V6" s="25">
+      <c r="V7" s="24">
         <f t="shared" si="0"/>
         <v>46143</v>
       </c>
-      <c r="W6" s="26">
-        <f>V6+1</f>
+      <c r="W7" s="25">
+        <f>V7+1</f>
         <v>46144</v>
       </c>
-      <c r="X6" s="24">
-        <f>W6+1</f>
+      <c r="X7" s="23">
+        <f>W7+1</f>
         <v>46145</v>
       </c>
-      <c r="Y6" s="24">
+      <c r="Y7" s="23">
         <f t="shared" si="0"/>
         <v>46146</v>
       </c>
-      <c r="Z6" s="24">
+      <c r="Z7" s="23">
         <f t="shared" si="0"/>
         <v>46147</v>
       </c>
-      <c r="AA6" s="24">
+      <c r="AA7" s="23">
         <f t="shared" si="0"/>
         <v>46148</v>
       </c>
-      <c r="AB6" s="24">
+      <c r="AB7" s="23">
         <f t="shared" si="0"/>
         <v>46149</v>
       </c>
-      <c r="AC6" s="25">
+      <c r="AC7" s="24">
         <f t="shared" si="0"/>
         <v>46150</v>
       </c>
     </row>
-    <row r="7" spans="1:30" s="19" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="85"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="I7" s="27" t="str">
-        <f t="shared" ref="I7:AC7" si="1">LEFT(TEXT(I6,"ddd"),1)</f>
+    <row r="8" spans="1:30" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="69"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="I8" s="26" t="str">
+        <f t="shared" ref="I8:AC8" si="1">LEFT(TEXT(I7,"ddd"),1)</f>
         <v>S</v>
       </c>
-      <c r="J7" s="28" t="str">
+      <c r="J8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="K7" s="28" t="str">
+      <c r="K8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="L7" s="28" t="str">
+      <c r="L8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>T</v>
       </c>
-      <c r="M7" s="28" t="str">
+      <c r="M8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="N7" s="28" t="str">
+      <c r="N8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>T</v>
       </c>
-      <c r="O7" s="28" t="str">
+      <c r="O8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>F</v>
       </c>
-      <c r="P7" s="28" t="str">
+      <c r="P8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="Q7" s="28" t="str">
+      <c r="Q8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="R7" s="28" t="str">
+      <c r="R8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="S7" s="28" t="str">
+      <c r="S8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>T</v>
       </c>
-      <c r="T7" s="28" t="str">
+      <c r="T8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="U7" s="28" t="str">
+      <c r="U8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>T</v>
       </c>
-      <c r="V7" s="28" t="str">
+      <c r="V8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>F</v>
       </c>
-      <c r="W7" s="28" t="str">
+      <c r="W8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="X7" s="28" t="str">
+      <c r="X8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="Y7" s="28" t="str">
+      <c r="Y8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="Z7" s="28" t="str">
+      <c r="Z8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>T</v>
       </c>
-      <c r="AA7" s="28" t="str">
+      <c r="AA8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>W</v>
       </c>
-      <c r="AB7" s="28" t="str">
+      <c r="AB8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>T</v>
       </c>
-      <c r="AC7" s="28" t="str">
+      <c r="AC8" s="27" t="str">
         <f t="shared" si="1"/>
         <v>F</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="19" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+    <row r="9" spans="1:30" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="H8" s="19" t="str">
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="H9" s="18" t="str">
         <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="31"/>
-      <c r="T8" s="31"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="31"/>
-      <c r="W8" s="31"/>
-      <c r="X8" s="31"/>
-      <c r="Y8" s="31"/>
-      <c r="Z8" s="31"/>
-      <c r="AA8" s="31"/>
-      <c r="AB8" s="31"/>
-      <c r="AC8" s="31"/>
-    </row>
-    <row r="9" spans="1:30" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7"/>
-      <c r="B9" s="32" t="s">
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="30"/>
+    </row>
+    <row r="10" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7"/>
+      <c r="B10" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="5" t="str">
-        <f t="shared" ref="H9:H26" si="2">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+      <c r="C10" s="32"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="5" t="str">
+        <f t="shared" ref="H10:H43" si="2">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="37"/>
-      <c r="T9" s="37"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="37"/>
-      <c r="W9" s="37"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="37"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="37"/>
-    </row>
-    <row r="10" spans="1:30" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="42">
-        <f>Project_Start</f>
-        <v>46130</v>
-      </c>
-      <c r="F10" s="42">
-        <f>E10+3</f>
-        <v>46133</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="5">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="43"/>
-      <c r="X10" s="43"/>
-      <c r="Y10" s="43"/>
-      <c r="Z10" s="43"/>
-      <c r="AA10" s="43"/>
-      <c r="AB10" s="43"/>
-      <c r="AC10" s="43"/>
-      <c r="AD10" s="72" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
+      <c r="S10" s="36"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="36"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="36"/>
+      <c r="AB10" s="36"/>
+      <c r="AC10" s="36"/>
+    </row>
+    <row r="11" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="47">
-        <f>F10</f>
-        <v>46133</v>
-      </c>
-      <c r="F11" s="47">
-        <f>E11+2</f>
-        <v>46135</v>
+      <c r="B11" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="39">
+        <v>1</v>
+      </c>
+      <c r="E11" s="40">
+        <v>46132</v>
+      </c>
+      <c r="F11" s="40">
+        <v>46132</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="48"/>
-      <c r="V11" s="48"/>
-      <c r="W11" s="43"/>
-      <c r="X11" s="43"/>
-      <c r="Y11" s="43"/>
-      <c r="Z11" s="43"/>
-      <c r="AA11" s="43"/>
-      <c r="AB11" s="43"/>
-      <c r="AC11" s="43"/>
-    </row>
-    <row r="12" spans="1:30" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="47">
-        <f>F11</f>
-        <v>46135</v>
-      </c>
-      <c r="F12" s="47">
-        <f>E12+4</f>
-        <v>46139</v>
+        <v>1</v>
+      </c>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="41"/>
+      <c r="Q11" s="41"/>
+      <c r="R11" s="41"/>
+      <c r="S11" s="41"/>
+      <c r="T11" s="41"/>
+      <c r="U11" s="41"/>
+      <c r="V11" s="41"/>
+      <c r="W11" s="41"/>
+      <c r="X11" s="41"/>
+      <c r="Y11" s="41"/>
+      <c r="Z11" s="41"/>
+      <c r="AA11" s="41"/>
+      <c r="AB11" s="41"/>
+      <c r="AC11" s="41"/>
+      <c r="AD11" s="68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7"/>
+      <c r="B12" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="90" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="43">
+        <v>0.25</v>
+      </c>
+      <c r="E12" s="44">
+        <v>46133</v>
+      </c>
+      <c r="F12" s="44">
+        <v>46143</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="5">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="43"/>
-      <c r="Y12" s="43"/>
-      <c r="Z12" s="43"/>
-      <c r="AA12" s="43"/>
-      <c r="AB12" s="43"/>
-      <c r="AC12" s="43"/>
-    </row>
-    <row r="13" spans="1:30" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="41"/>
+      <c r="Q12" s="41"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="41"/>
+      <c r="T12" s="41"/>
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="41"/>
+      <c r="X12" s="41"/>
+      <c r="Y12" s="41"/>
+      <c r="Z12" s="41"/>
+      <c r="AA12" s="41"/>
+      <c r="AB12" s="41"/>
+      <c r="AC12" s="41"/>
+    </row>
+    <row r="13" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="47">
-        <f>F12</f>
-        <v>46139</v>
-      </c>
-      <c r="F13" s="47">
-        <f>E13+5</f>
-        <v>46144</v>
-      </c>
+      <c r="B13" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="90" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="5">
+      <c r="H13" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="43"/>
-      <c r="W13" s="43"/>
-      <c r="X13" s="43"/>
-      <c r="Y13" s="48"/>
-      <c r="Z13" s="43"/>
-      <c r="AA13" s="43"/>
-      <c r="AB13" s="43"/>
-      <c r="AC13" s="43"/>
-    </row>
-    <row r="14" spans="1:30" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v/>
+      </c>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="41"/>
+      <c r="Q13" s="41"/>
+      <c r="R13" s="41"/>
+      <c r="S13" s="41"/>
+      <c r="T13" s="41"/>
+      <c r="U13" s="41"/>
+      <c r="V13" s="41"/>
+      <c r="W13" s="41"/>
+      <c r="X13" s="41"/>
+      <c r="Y13" s="41"/>
+      <c r="Z13" s="41"/>
+      <c r="AA13" s="41"/>
+      <c r="AB13" s="41"/>
+      <c r="AC13" s="41"/>
+    </row>
+    <row r="14" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="47">
-        <f>E11+1</f>
-        <v>46134</v>
-      </c>
-      <c r="F14" s="47">
-        <f>E14+2</f>
-        <v>46136</v>
+      <c r="B14" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="90"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="44">
+        <v>46137</v>
+      </c>
+      <c r="F14" s="44">
+        <v>46143</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="43"/>
-      <c r="Y14" s="43"/>
-      <c r="Z14" s="43"/>
-      <c r="AA14" s="43"/>
-      <c r="AB14" s="43"/>
-      <c r="AC14" s="43"/>
-    </row>
-    <row r="15" spans="1:30" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7"/>
-      <c r="B15" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="41"/>
+      <c r="R14" s="41"/>
+      <c r="S14" s="41"/>
+      <c r="T14" s="41"/>
+      <c r="U14" s="41"/>
+      <c r="V14" s="41"/>
+      <c r="W14" s="41"/>
+      <c r="X14" s="41"/>
+      <c r="Y14" s="45"/>
+      <c r="Z14" s="41"/>
+      <c r="AA14" s="41"/>
+      <c r="AB14" s="41"/>
+      <c r="AC14" s="41"/>
+    </row>
+    <row r="15" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6"/>
+      <c r="B15" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="90"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="44">
+        <v>46137</v>
+      </c>
+      <c r="F15" s="44">
+        <v>46143</v>
+      </c>
+      <c r="G15" s="10"/>
+      <c r="H15" s="5">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="41"/>
+      <c r="S15" s="41"/>
+      <c r="T15" s="41"/>
+      <c r="U15" s="41"/>
+      <c r="V15" s="41"/>
+      <c r="W15" s="41"/>
+      <c r="X15" s="41"/>
+      <c r="Y15" s="41"/>
+      <c r="Z15" s="41"/>
+      <c r="AA15" s="41"/>
+      <c r="AB15" s="41"/>
+      <c r="AC15" s="41"/>
+    </row>
+    <row r="16" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="6"/>
+      <c r="B16" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="91" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="87">
+        <v>1</v>
+      </c>
+      <c r="E16" s="88">
+        <v>46137</v>
+      </c>
+      <c r="F16" s="103">
+        <v>46137</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="41"/>
+      <c r="T16" s="41"/>
+      <c r="U16" s="41"/>
+      <c r="V16" s="41"/>
+      <c r="W16" s="41"/>
+      <c r="X16" s="41"/>
+      <c r="Y16" s="41"/>
+      <c r="Z16" s="41"/>
+      <c r="AA16" s="41"/>
+      <c r="AB16" s="41"/>
+      <c r="AC16" s="41"/>
+    </row>
+    <row r="17" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="93"/>
+      <c r="B17" s="101" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="104" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="102">
+        <v>1</v>
+      </c>
+      <c r="E17" s="103">
+        <v>46137</v>
+      </c>
+      <c r="F17" s="103">
+        <v>46137</v>
+      </c>
+      <c r="G17" s="94"/>
+      <c r="H17" s="92"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="96"/>
+      <c r="O17" s="96"/>
+      <c r="P17" s="96"/>
+      <c r="Q17" s="96"/>
+      <c r="R17" s="96"/>
+      <c r="S17" s="96"/>
+      <c r="T17" s="96"/>
+      <c r="U17" s="96"/>
+      <c r="V17" s="96"/>
+      <c r="W17" s="96"/>
+      <c r="X17" s="96"/>
+      <c r="Y17" s="96"/>
+      <c r="Z17" s="96"/>
+      <c r="AA17" s="96"/>
+      <c r="AB17" s="96"/>
+      <c r="AC17" s="96"/>
+    </row>
+    <row r="18" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="7"/>
+      <c r="B18" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="5" t="str">
+      <c r="C18" s="47"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="5" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:30" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="7"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="E16" s="57">
-        <f>E14+1</f>
-        <v>46135</v>
-      </c>
-      <c r="F16" s="57">
-        <f>E16+4</f>
-        <v>46139</v>
-      </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="5">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="43"/>
-      <c r="Y16" s="43"/>
-      <c r="Z16" s="43"/>
-      <c r="AA16" s="43"/>
-      <c r="AB16" s="43"/>
-      <c r="AC16" s="43"/>
-    </row>
-    <row r="17" spans="1:29" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="6"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="56">
-        <v>0.5</v>
-      </c>
-      <c r="E17" s="57">
-        <f>E16+2</f>
+    <row r="19" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="7"/>
+      <c r="B19" s="97" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="53"/>
+      <c r="E19" s="54">
         <v>46137</v>
       </c>
-      <c r="F17" s="57">
-        <f>E17+5</f>
-        <v>46142</v>
-      </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="5">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="48"/>
-      <c r="V17" s="48"/>
-      <c r="W17" s="43"/>
-      <c r="X17" s="43"/>
-      <c r="Y17" s="43"/>
-      <c r="Z17" s="43"/>
-      <c r="AA17" s="43"/>
-      <c r="AB17" s="43"/>
-      <c r="AC17" s="43"/>
-    </row>
-    <row r="18" spans="1:29" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="6"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="57">
-        <f>F17</f>
-        <v>46142</v>
-      </c>
-      <c r="F18" s="57">
-        <f>E18+3</f>
-        <v>46145</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="5">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="43"/>
-      <c r="S18" s="43"/>
-      <c r="T18" s="43"/>
-      <c r="U18" s="43"/>
-      <c r="V18" s="43"/>
-      <c r="W18" s="43"/>
-      <c r="X18" s="43"/>
-      <c r="Y18" s="43"/>
-      <c r="Z18" s="43"/>
-      <c r="AA18" s="43"/>
-      <c r="AB18" s="43"/>
-      <c r="AC18" s="43"/>
-    </row>
-    <row r="19" spans="1:29" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="6"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="57">
-        <f>E18</f>
-        <v>46142</v>
-      </c>
-      <c r="F19" s="57">
-        <f>E19+2</f>
-        <v>46144</v>
+      <c r="F19" s="54">
+        <v>46143</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43"/>
-      <c r="U19" s="43"/>
-      <c r="V19" s="43"/>
-      <c r="W19" s="43"/>
-      <c r="X19" s="43"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="43"/>
-      <c r="AA19" s="43"/>
-      <c r="AB19" s="43"/>
-      <c r="AC19" s="43"/>
-    </row>
-    <row r="20" spans="1:29" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="41"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="41"/>
+      <c r="U19" s="41"/>
+      <c r="V19" s="41"/>
+      <c r="W19" s="41"/>
+      <c r="X19" s="41"/>
+      <c r="Y19" s="41"/>
+      <c r="Z19" s="41"/>
+      <c r="AA19" s="41"/>
+      <c r="AB19" s="41"/>
+      <c r="AC19" s="41"/>
+    </row>
+    <row r="20" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="57">
-        <f>E19</f>
-        <v>46142</v>
-      </c>
-      <c r="F20" s="57">
-        <f>E20+3</f>
-        <v>46145</v>
+      <c r="B20" s="97" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="53"/>
+      <c r="E20" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F20" s="100">
+        <v>46143</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="43"/>
-      <c r="R20" s="43"/>
-      <c r="S20" s="43"/>
-      <c r="T20" s="43"/>
-      <c r="U20" s="43"/>
-      <c r="V20" s="43"/>
-      <c r="W20" s="43"/>
-      <c r="X20" s="43"/>
-      <c r="Y20" s="43"/>
-      <c r="Z20" s="43"/>
-      <c r="AA20" s="43"/>
-      <c r="AB20" s="43"/>
-      <c r="AC20" s="43"/>
-    </row>
-    <row r="21" spans="1:29" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="41"/>
+      <c r="S20" s="41"/>
+      <c r="T20" s="41"/>
+      <c r="U20" s="45"/>
+      <c r="V20" s="45"/>
+      <c r="W20" s="41"/>
+      <c r="X20" s="41"/>
+      <c r="Y20" s="41"/>
+      <c r="Z20" s="41"/>
+      <c r="AA20" s="41"/>
+      <c r="AB20" s="41"/>
+      <c r="AC20" s="41"/>
+    </row>
+    <row r="21" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6"/>
-      <c r="B21" s="58" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="59"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="62"/>
+      <c r="B21" s="97" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="53"/>
+      <c r="E21" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F21" s="100">
+        <v>46143</v>
+      </c>
       <c r="G21" s="10"/>
-      <c r="H21" s="5" t="str">
+      <c r="H21" s="5">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="I21" s="63"/>
-      <c r="J21" s="63"/>
-      <c r="K21" s="63"/>
-      <c r="L21" s="63"/>
-      <c r="M21" s="63"/>
-      <c r="N21" s="63"/>
-      <c r="O21" s="63"/>
-      <c r="P21" s="63"/>
-      <c r="Q21" s="63"/>
-      <c r="R21" s="63"/>
-      <c r="S21" s="63"/>
-      <c r="T21" s="63"/>
-      <c r="U21" s="63"/>
-      <c r="V21" s="63"/>
-      <c r="W21" s="63"/>
-      <c r="X21" s="63"/>
-      <c r="Y21" s="63"/>
-      <c r="Z21" s="63"/>
-      <c r="AA21" s="63"/>
-      <c r="AB21" s="63"/>
-      <c r="AC21" s="63"/>
-    </row>
-    <row r="22" spans="1:29" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="41"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="41"/>
+      <c r="R21" s="41"/>
+      <c r="S21" s="41"/>
+      <c r="T21" s="41"/>
+      <c r="U21" s="41"/>
+      <c r="V21" s="41"/>
+      <c r="W21" s="41"/>
+      <c r="X21" s="41"/>
+      <c r="Y21" s="41"/>
+      <c r="Z21" s="41"/>
+      <c r="AA21" s="41"/>
+      <c r="AB21" s="41"/>
+      <c r="AC21" s="41"/>
+    </row>
+    <row r="22" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6"/>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="66">
-        <v>0.5</v>
-      </c>
-      <c r="E22" s="67">
-        <f>E10+15</f>
-        <v>46145</v>
-      </c>
-      <c r="F22" s="67">
-        <f>E22+5</f>
-        <v>46150</v>
+      <c r="B22" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="98" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="53"/>
+      <c r="E22" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F22" s="100">
+        <v>46143</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="5">
         <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="43"/>
-      <c r="R22" s="43"/>
-      <c r="S22" s="43"/>
-      <c r="T22" s="43"/>
-      <c r="U22" s="43"/>
-      <c r="V22" s="43"/>
-      <c r="W22" s="43"/>
-      <c r="X22" s="43"/>
-      <c r="Y22" s="43"/>
-      <c r="Z22" s="43"/>
-      <c r="AA22" s="43"/>
-      <c r="AB22" s="43"/>
-      <c r="AC22" s="43"/>
-    </row>
-    <row r="23" spans="1:29" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="41"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="41"/>
+      <c r="R22" s="41"/>
+      <c r="S22" s="41"/>
+      <c r="T22" s="41"/>
+      <c r="U22" s="41"/>
+      <c r="V22" s="41"/>
+      <c r="W22" s="41"/>
+      <c r="X22" s="41"/>
+      <c r="Y22" s="45"/>
+      <c r="Z22" s="41"/>
+      <c r="AA22" s="41"/>
+      <c r="AB22" s="41"/>
+      <c r="AC22" s="41"/>
+    </row>
+    <row r="23" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="66">
-        <v>0.6</v>
-      </c>
-      <c r="E23" s="67">
-        <f>F22+1</f>
-        <v>46151</v>
-      </c>
-      <c r="F23" s="67">
-        <f>E23+4</f>
-        <v>46155</v>
+      <c r="B23" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="53"/>
+      <c r="E23" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F23" s="100">
+        <v>46143</v>
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="5">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="43"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="43"/>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="43"/>
-      <c r="R23" s="43"/>
-      <c r="S23" s="43"/>
-      <c r="T23" s="43"/>
-      <c r="U23" s="43"/>
-      <c r="V23" s="43"/>
-      <c r="W23" s="43"/>
-      <c r="X23" s="43"/>
-      <c r="Y23" s="43"/>
-      <c r="Z23" s="43"/>
-      <c r="AA23" s="43"/>
-      <c r="AB23" s="43"/>
-      <c r="AC23" s="43"/>
-    </row>
-    <row r="24" spans="1:29" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="6"/>
-      <c r="B24" s="64"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="66">
-        <v>0.5</v>
-      </c>
-      <c r="E24" s="67">
-        <f>E23+5</f>
-        <v>46156</v>
-      </c>
-      <c r="F24" s="67">
-        <f>E24+5</f>
-        <v>46161</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="5">
+        <v>7</v>
+      </c>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="41"/>
+      <c r="L23" s="41"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="41"/>
+      <c r="O23" s="41"/>
+      <c r="P23" s="41"/>
+      <c r="Q23" s="41"/>
+      <c r="R23" s="41"/>
+      <c r="S23" s="41"/>
+      <c r="T23" s="41"/>
+      <c r="U23" s="41"/>
+      <c r="V23" s="41"/>
+      <c r="W23" s="41"/>
+      <c r="X23" s="41"/>
+      <c r="Y23" s="41"/>
+      <c r="Z23" s="41"/>
+      <c r="AA23" s="41"/>
+      <c r="AB23" s="41"/>
+      <c r="AC23" s="41"/>
+    </row>
+    <row r="24" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="93"/>
+      <c r="B24" s="97" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="98" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="99"/>
+      <c r="E24" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F24" s="100">
+        <v>46143</v>
+      </c>
+      <c r="G24" s="94"/>
+      <c r="H24" s="92"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="96"/>
+      <c r="K24" s="96"/>
+      <c r="L24" s="96"/>
+      <c r="M24" s="96"/>
+      <c r="N24" s="96"/>
+      <c r="O24" s="96"/>
+      <c r="P24" s="96"/>
+      <c r="Q24" s="96"/>
+      <c r="R24" s="96"/>
+      <c r="S24" s="96"/>
+      <c r="T24" s="96"/>
+      <c r="U24" s="96"/>
+      <c r="V24" s="96"/>
+      <c r="W24" s="96"/>
+      <c r="X24" s="96"/>
+      <c r="Y24" s="96"/>
+      <c r="Z24" s="96"/>
+      <c r="AA24" s="96"/>
+      <c r="AB24" s="96"/>
+      <c r="AC24" s="96"/>
+    </row>
+    <row r="25" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="93"/>
+      <c r="B25" s="97" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="98" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="99"/>
+      <c r="E25" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F25" s="100">
+        <v>46143</v>
+      </c>
+      <c r="G25" s="94"/>
+      <c r="H25" s="92"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="96"/>
+      <c r="L25" s="96"/>
+      <c r="M25" s="96"/>
+      <c r="N25" s="96"/>
+      <c r="O25" s="96"/>
+      <c r="P25" s="96"/>
+      <c r="Q25" s="96"/>
+      <c r="R25" s="96"/>
+      <c r="S25" s="96"/>
+      <c r="T25" s="96"/>
+      <c r="U25" s="96"/>
+      <c r="V25" s="96"/>
+      <c r="W25" s="96"/>
+      <c r="X25" s="96"/>
+      <c r="Y25" s="96"/>
+      <c r="Z25" s="96"/>
+      <c r="AA25" s="96"/>
+      <c r="AB25" s="96"/>
+      <c r="AC25" s="96"/>
+    </row>
+    <row r="26" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="93"/>
+      <c r="B26" s="97" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="98" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="99"/>
+      <c r="E26" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F26" s="100">
+        <v>46143</v>
+      </c>
+      <c r="G26" s="94"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="96"/>
+      <c r="J26" s="96"/>
+      <c r="K26" s="96"/>
+      <c r="L26" s="96"/>
+      <c r="M26" s="96"/>
+      <c r="N26" s="96"/>
+      <c r="O26" s="96"/>
+      <c r="P26" s="96"/>
+      <c r="Q26" s="96"/>
+      <c r="R26" s="96"/>
+      <c r="S26" s="96"/>
+      <c r="T26" s="96"/>
+      <c r="U26" s="96"/>
+      <c r="V26" s="96"/>
+      <c r="W26" s="96"/>
+      <c r="X26" s="96"/>
+      <c r="Y26" s="96"/>
+      <c r="Z26" s="96"/>
+      <c r="AA26" s="96"/>
+      <c r="AB26" s="96"/>
+      <c r="AC26" s="96"/>
+    </row>
+    <row r="27" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="93"/>
+      <c r="B27" s="97" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="98" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="99"/>
+      <c r="E27" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F27" s="100">
+        <v>46143</v>
+      </c>
+      <c r="G27" s="94"/>
+      <c r="H27" s="92"/>
+      <c r="I27" s="96"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="96"/>
+      <c r="L27" s="96"/>
+      <c r="M27" s="96"/>
+      <c r="N27" s="96"/>
+      <c r="O27" s="96"/>
+      <c r="P27" s="96"/>
+      <c r="Q27" s="96"/>
+      <c r="R27" s="96"/>
+      <c r="S27" s="96"/>
+      <c r="T27" s="96"/>
+      <c r="U27" s="96"/>
+      <c r="V27" s="96"/>
+      <c r="W27" s="96"/>
+      <c r="X27" s="96"/>
+      <c r="Y27" s="96"/>
+      <c r="Z27" s="96"/>
+      <c r="AA27" s="96"/>
+      <c r="AB27" s="96"/>
+      <c r="AC27" s="96"/>
+    </row>
+    <row r="28" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="93"/>
+      <c r="B28" s="97" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="98" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="99"/>
+      <c r="E28" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F28" s="100">
+        <v>46143</v>
+      </c>
+      <c r="G28" s="94"/>
+      <c r="H28" s="92"/>
+      <c r="I28" s="96"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="96"/>
+      <c r="L28" s="96"/>
+      <c r="M28" s="96"/>
+      <c r="N28" s="96"/>
+      <c r="O28" s="96"/>
+      <c r="P28" s="96"/>
+      <c r="Q28" s="96"/>
+      <c r="R28" s="96"/>
+      <c r="S28" s="96"/>
+      <c r="T28" s="96"/>
+      <c r="U28" s="96"/>
+      <c r="V28" s="96"/>
+      <c r="W28" s="96"/>
+      <c r="X28" s="96"/>
+      <c r="Y28" s="96"/>
+      <c r="Z28" s="96"/>
+      <c r="AA28" s="96"/>
+      <c r="AB28" s="96"/>
+      <c r="AC28" s="96"/>
+    </row>
+    <row r="29" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="93"/>
+      <c r="B29" s="97" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="98" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="99"/>
+      <c r="E29" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F29" s="100">
+        <v>46143</v>
+      </c>
+      <c r="G29" s="94"/>
+      <c r="H29" s="92"/>
+      <c r="I29" s="96"/>
+      <c r="J29" s="96"/>
+      <c r="K29" s="96"/>
+      <c r="L29" s="96"/>
+      <c r="M29" s="96"/>
+      <c r="N29" s="96"/>
+      <c r="O29" s="96"/>
+      <c r="P29" s="96"/>
+      <c r="Q29" s="96"/>
+      <c r="R29" s="96"/>
+      <c r="S29" s="96"/>
+      <c r="T29" s="96"/>
+      <c r="U29" s="96"/>
+      <c r="V29" s="96"/>
+      <c r="W29" s="96"/>
+      <c r="X29" s="96"/>
+      <c r="Y29" s="96"/>
+      <c r="Z29" s="96"/>
+      <c r="AA29" s="96"/>
+      <c r="AB29" s="96"/>
+      <c r="AC29" s="96"/>
+    </row>
+    <row r="30" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="93"/>
+      <c r="B30" s="97" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="98" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="99"/>
+      <c r="E30" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F30" s="100">
+        <v>46143</v>
+      </c>
+      <c r="G30" s="94"/>
+      <c r="H30" s="92"/>
+      <c r="I30" s="96"/>
+      <c r="J30" s="96"/>
+      <c r="K30" s="96"/>
+      <c r="L30" s="96"/>
+      <c r="M30" s="96"/>
+      <c r="N30" s="96"/>
+      <c r="O30" s="96"/>
+      <c r="P30" s="96"/>
+      <c r="Q30" s="96"/>
+      <c r="R30" s="96"/>
+      <c r="S30" s="96"/>
+      <c r="T30" s="96"/>
+      <c r="U30" s="96"/>
+      <c r="V30" s="96"/>
+      <c r="W30" s="96"/>
+      <c r="X30" s="96"/>
+      <c r="Y30" s="96"/>
+      <c r="Z30" s="96"/>
+      <c r="AA30" s="96"/>
+      <c r="AB30" s="96"/>
+      <c r="AC30" s="96"/>
+    </row>
+    <row r="31" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="93"/>
+      <c r="B31" s="97" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="98" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="99"/>
+      <c r="E31" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F31" s="100">
+        <v>46143</v>
+      </c>
+      <c r="G31" s="94"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="96"/>
+      <c r="L31" s="96"/>
+      <c r="M31" s="96"/>
+      <c r="N31" s="96"/>
+      <c r="O31" s="96"/>
+      <c r="P31" s="96"/>
+      <c r="Q31" s="96"/>
+      <c r="R31" s="96"/>
+      <c r="S31" s="96"/>
+      <c r="T31" s="96"/>
+      <c r="U31" s="96"/>
+      <c r="V31" s="96"/>
+      <c r="W31" s="96"/>
+      <c r="X31" s="96"/>
+      <c r="Y31" s="96"/>
+      <c r="Z31" s="96"/>
+      <c r="AA31" s="96"/>
+      <c r="AB31" s="96"/>
+      <c r="AC31" s="96"/>
+    </row>
+    <row r="32" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="93"/>
+      <c r="B32" s="97" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="98" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="99"/>
+      <c r="E32" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F32" s="100">
+        <v>46143</v>
+      </c>
+      <c r="G32" s="94"/>
+      <c r="H32" s="92"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="96"/>
+      <c r="K32" s="96"/>
+      <c r="L32" s="96"/>
+      <c r="M32" s="96"/>
+      <c r="N32" s="96"/>
+      <c r="O32" s="96"/>
+      <c r="P32" s="96"/>
+      <c r="Q32" s="96"/>
+      <c r="R32" s="96"/>
+      <c r="S32" s="96"/>
+      <c r="T32" s="96"/>
+      <c r="U32" s="96"/>
+      <c r="V32" s="96"/>
+      <c r="W32" s="96"/>
+      <c r="X32" s="96"/>
+      <c r="Y32" s="96"/>
+      <c r="Z32" s="96"/>
+      <c r="AA32" s="96"/>
+      <c r="AB32" s="96"/>
+      <c r="AC32" s="96"/>
+    </row>
+    <row r="33" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="93"/>
+      <c r="B33" s="97" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="98" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="99"/>
+      <c r="E33" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F33" s="100">
+        <v>46143</v>
+      </c>
+      <c r="G33" s="94"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="96"/>
+      <c r="J33" s="96"/>
+      <c r="K33" s="96"/>
+      <c r="L33" s="96"/>
+      <c r="M33" s="96"/>
+      <c r="N33" s="96"/>
+      <c r="O33" s="96"/>
+      <c r="P33" s="96"/>
+      <c r="Q33" s="96"/>
+      <c r="R33" s="96"/>
+      <c r="S33" s="96"/>
+      <c r="T33" s="96"/>
+      <c r="U33" s="96"/>
+      <c r="V33" s="96"/>
+      <c r="W33" s="96"/>
+      <c r="X33" s="96"/>
+      <c r="Y33" s="96"/>
+      <c r="Z33" s="96"/>
+      <c r="AA33" s="96"/>
+      <c r="AB33" s="96"/>
+      <c r="AC33" s="96"/>
+    </row>
+    <row r="34" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="93"/>
+      <c r="B34" s="97" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="98" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="99"/>
+      <c r="E34" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F34" s="100">
+        <v>46143</v>
+      </c>
+      <c r="G34" s="94"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="96"/>
+      <c r="J34" s="96"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="96"/>
+      <c r="M34" s="96"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="96"/>
+      <c r="P34" s="96"/>
+      <c r="Q34" s="96"/>
+      <c r="R34" s="96"/>
+      <c r="S34" s="96"/>
+      <c r="T34" s="96"/>
+      <c r="U34" s="96"/>
+      <c r="V34" s="96"/>
+      <c r="W34" s="96"/>
+      <c r="X34" s="96"/>
+      <c r="Y34" s="96"/>
+      <c r="Z34" s="96"/>
+      <c r="AA34" s="96"/>
+      <c r="AB34" s="96"/>
+      <c r="AC34" s="96"/>
+    </row>
+    <row r="35" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="93"/>
+      <c r="B35" s="97" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="98" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="99"/>
+      <c r="E35" s="100">
+        <v>46137</v>
+      </c>
+      <c r="F35" s="100">
+        <v>46143</v>
+      </c>
+      <c r="G35" s="94"/>
+      <c r="H35" s="92"/>
+      <c r="I35" s="96"/>
+      <c r="J35" s="96"/>
+      <c r="K35" s="96"/>
+      <c r="L35" s="96"/>
+      <c r="M35" s="96"/>
+      <c r="N35" s="96"/>
+      <c r="O35" s="96"/>
+      <c r="P35" s="96"/>
+      <c r="Q35" s="96"/>
+      <c r="R35" s="96"/>
+      <c r="S35" s="96"/>
+      <c r="T35" s="96"/>
+      <c r="U35" s="96"/>
+      <c r="V35" s="96"/>
+      <c r="W35" s="96"/>
+      <c r="X35" s="96"/>
+      <c r="Y35" s="96"/>
+      <c r="Z35" s="96"/>
+      <c r="AA35" s="96"/>
+      <c r="AB35" s="96"/>
+      <c r="AC35" s="96"/>
+    </row>
+    <row r="36" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="93"/>
+      <c r="B36" s="97"/>
+      <c r="C36" s="98"/>
+      <c r="D36" s="99"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="100"/>
+      <c r="G36" s="94"/>
+      <c r="H36" s="92"/>
+      <c r="I36" s="96"/>
+      <c r="J36" s="96"/>
+      <c r="K36" s="96"/>
+      <c r="L36" s="96"/>
+      <c r="M36" s="96"/>
+      <c r="N36" s="96"/>
+      <c r="O36" s="96"/>
+      <c r="P36" s="96"/>
+      <c r="Q36" s="96"/>
+      <c r="R36" s="96"/>
+      <c r="S36" s="96"/>
+      <c r="T36" s="96"/>
+      <c r="U36" s="96"/>
+      <c r="V36" s="96"/>
+      <c r="W36" s="96"/>
+      <c r="X36" s="96"/>
+      <c r="Y36" s="96"/>
+      <c r="Z36" s="96"/>
+      <c r="AA36" s="96"/>
+      <c r="AB36" s="96"/>
+      <c r="AC36" s="96"/>
+    </row>
+    <row r="37" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="93"/>
+      <c r="B37" s="97"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="99"/>
+      <c r="E37" s="100"/>
+      <c r="F37" s="100"/>
+      <c r="G37" s="94"/>
+      <c r="H37" s="92"/>
+      <c r="I37" s="96"/>
+      <c r="J37" s="96"/>
+      <c r="K37" s="96"/>
+      <c r="L37" s="96"/>
+      <c r="M37" s="96"/>
+      <c r="N37" s="96"/>
+      <c r="O37" s="96"/>
+      <c r="P37" s="96"/>
+      <c r="Q37" s="96"/>
+      <c r="R37" s="96"/>
+      <c r="S37" s="96"/>
+      <c r="T37" s="96"/>
+      <c r="U37" s="96"/>
+      <c r="V37" s="96"/>
+      <c r="W37" s="96"/>
+      <c r="X37" s="96"/>
+      <c r="Y37" s="96"/>
+      <c r="Z37" s="96"/>
+      <c r="AA37" s="96"/>
+      <c r="AB37" s="96"/>
+      <c r="AC37" s="96"/>
+    </row>
+    <row r="38" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6"/>
+      <c r="B38" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="56"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="43"/>
-      <c r="R24" s="43"/>
-      <c r="S24" s="43"/>
-      <c r="T24" s="43"/>
-      <c r="U24" s="43"/>
-      <c r="V24" s="43"/>
-      <c r="W24" s="43"/>
-      <c r="X24" s="43"/>
-      <c r="Y24" s="43"/>
-      <c r="Z24" s="43"/>
-      <c r="AA24" s="43"/>
-      <c r="AB24" s="43"/>
-      <c r="AC24" s="43"/>
-    </row>
-    <row r="25" spans="1:29" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="6"/>
-      <c r="B25" s="64"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="66">
-        <v>0.25</v>
-      </c>
-      <c r="E25" s="67">
-        <f>F24+1</f>
-        <v>46162</v>
-      </c>
-      <c r="F25" s="67">
-        <f>E25+4</f>
-        <v>46166</v>
-      </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="5">
+        <v/>
+      </c>
+      <c r="I38" s="60"/>
+      <c r="J38" s="60"/>
+      <c r="K38" s="60"/>
+      <c r="L38" s="60"/>
+      <c r="M38" s="60"/>
+      <c r="N38" s="60"/>
+      <c r="O38" s="60"/>
+      <c r="P38" s="60"/>
+      <c r="Q38" s="60"/>
+      <c r="R38" s="60"/>
+      <c r="S38" s="60"/>
+      <c r="T38" s="60"/>
+      <c r="U38" s="60"/>
+      <c r="V38" s="60"/>
+      <c r="W38" s="60"/>
+      <c r="X38" s="60"/>
+      <c r="Y38" s="60"/>
+      <c r="Z38" s="60"/>
+      <c r="AA38" s="60"/>
+      <c r="AB38" s="60"/>
+      <c r="AC38" s="60"/>
+    </row>
+    <row r="39" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="6"/>
+      <c r="B39" s="61"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="43"/>
-      <c r="T25" s="43"/>
-      <c r="U25" s="43"/>
-      <c r="V25" s="43"/>
-      <c r="W25" s="43"/>
-      <c r="X25" s="43"/>
-      <c r="Y25" s="43"/>
-      <c r="Z25" s="43"/>
-      <c r="AA25" s="43"/>
-      <c r="AB25" s="43"/>
-      <c r="AC25" s="43"/>
-    </row>
-    <row r="26" spans="1:29" s="38" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="6"/>
-      <c r="B26" s="64"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="66">
-        <v>0.25</v>
-      </c>
-      <c r="E26" s="67">
-        <f>E24</f>
-        <v>46156</v>
-      </c>
-      <c r="F26" s="67">
-        <f>E26+4</f>
-        <v>46160</v>
-      </c>
-      <c r="G26" s="10"/>
-      <c r="H26" s="5">
+        <v/>
+      </c>
+      <c r="I39" s="41"/>
+      <c r="J39" s="41"/>
+      <c r="K39" s="41"/>
+      <c r="L39" s="41"/>
+      <c r="M39" s="41"/>
+      <c r="N39" s="41"/>
+      <c r="O39" s="41"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="41"/>
+      <c r="S39" s="41"/>
+      <c r="T39" s="41"/>
+      <c r="U39" s="41"/>
+      <c r="V39" s="41"/>
+      <c r="W39" s="41"/>
+      <c r="X39" s="41"/>
+      <c r="Y39" s="41"/>
+      <c r="Z39" s="41"/>
+      <c r="AA39" s="41"/>
+      <c r="AB39" s="41"/>
+      <c r="AC39" s="41"/>
+    </row>
+    <row r="40" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="6"/>
+      <c r="B40" s="61"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I26" s="43"/>
-      <c r="J26" s="43"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="43"/>
-      <c r="M26" s="43"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="43"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="X26" s="43"/>
-      <c r="Y26" s="43"/>
-      <c r="Z26" s="43"/>
-      <c r="AA26" s="43"/>
-      <c r="AB26" s="43"/>
-      <c r="AC26" s="43"/>
-    </row>
-    <row r="27" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="9"/>
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="4"/>
+        <v/>
+      </c>
+      <c r="I40" s="41"/>
+      <c r="J40" s="41"/>
+      <c r="K40" s="41"/>
+      <c r="L40" s="41"/>
+      <c r="M40" s="41"/>
+      <c r="N40" s="41"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="41"/>
+      <c r="S40" s="41"/>
+      <c r="T40" s="41"/>
+      <c r="U40" s="41"/>
+      <c r="V40" s="41"/>
+      <c r="W40" s="41"/>
+      <c r="X40" s="41"/>
+      <c r="Y40" s="41"/>
+      <c r="Z40" s="41"/>
+      <c r="AA40" s="41"/>
+      <c r="AB40" s="41"/>
+      <c r="AC40" s="41"/>
+    </row>
+    <row r="41" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="6"/>
+      <c r="B41" s="61"/>
+      <c r="C41" s="62"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="I41" s="41"/>
+      <c r="J41" s="41"/>
+      <c r="K41" s="41"/>
+      <c r="L41" s="41"/>
+      <c r="M41" s="41"/>
+      <c r="N41" s="41"/>
+      <c r="O41" s="41"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="41"/>
+      <c r="S41" s="41"/>
+      <c r="T41" s="41"/>
+      <c r="U41" s="41"/>
+      <c r="V41" s="41"/>
+      <c r="W41" s="41"/>
+      <c r="X41" s="41"/>
+      <c r="Y41" s="41"/>
+      <c r="Z41" s="41"/>
+      <c r="AA41" s="41"/>
+      <c r="AB41" s="41"/>
+      <c r="AC41" s="41"/>
+    </row>
+    <row r="42" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="6"/>
+      <c r="B42" s="61"/>
+      <c r="C42" s="62"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="I42" s="41"/>
+      <c r="J42" s="41"/>
+      <c r="K42" s="41"/>
+      <c r="L42" s="41"/>
+      <c r="M42" s="41"/>
+      <c r="N42" s="41"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="41"/>
+      <c r="S42" s="41"/>
+      <c r="T42" s="41"/>
+      <c r="U42" s="41"/>
+      <c r="V42" s="41"/>
+      <c r="W42" s="41"/>
+      <c r="X42" s="41"/>
+      <c r="Y42" s="41"/>
+      <c r="Z42" s="41"/>
+      <c r="AA42" s="41"/>
+      <c r="AB42" s="41"/>
+      <c r="AC42" s="41"/>
+    </row>
+    <row r="43" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="6"/>
+      <c r="B43" s="61"/>
+      <c r="C43" s="62"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="64"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="I43" s="41"/>
+      <c r="J43" s="41"/>
+      <c r="K43" s="41"/>
+      <c r="L43" s="41"/>
+      <c r="M43" s="41"/>
+      <c r="N43" s="41"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="41"/>
+      <c r="S43" s="41"/>
+      <c r="T43" s="41"/>
+      <c r="U43" s="41"/>
+      <c r="V43" s="41"/>
+      <c r="W43" s="41"/>
+      <c r="X43" s="41"/>
+      <c r="Y43" s="41"/>
+      <c r="Z43" s="41"/>
+      <c r="AA43" s="41"/>
+      <c r="AB43" s="41"/>
+      <c r="AC43" s="41"/>
+    </row>
+    <row r="44" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G44" s="3"/>
+    </row>
+    <row r="45" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="9"/>
+      <c r="F45" s="8"/>
+    </row>
+    <row r="46" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C46" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="P6:V6"/>
+    <mergeCell ref="W6:AC6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="Q2:Z2"/>
     <mergeCell ref="Q1:Z1"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="I2:O2"/>
     <mergeCell ref="I3:O3"/>
     <mergeCell ref="Q3:Z3"/>
-    <mergeCell ref="I5:O5"/>
-    <mergeCell ref="P5:V5"/>
-    <mergeCell ref="W5:AC5"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8:D26">
+  <conditionalFormatting sqref="D9:D43">
     <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2630,70 +3443,79 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:AB26">
+  <conditionalFormatting sqref="I6:AB43">
     <cfRule type="expression" dxfId="13" priority="1">
-      <formula>AND(TODAY()&gt;=I$6, TODAY()&lt;J$6)</formula>
+      <formula>AND(TODAY()&gt;=I$7, TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10:AB14">
+  <conditionalFormatting sqref="I11:AB17">
     <cfRule type="expression" dxfId="12" priority="6">
-      <formula>AND(task_start&lt;=I$6,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$6)</formula>
+      <formula>AND(task_start&lt;=I$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$7)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="7" stopIfTrue="1">
-      <formula>AND(task_end&gt;=I$6,task_start&lt;J$6)</formula>
+      <formula>AND(task_end&gt;=I$7,task_start&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16:AB20">
+  <conditionalFormatting sqref="I19:AB37">
     <cfRule type="expression" dxfId="10" priority="4">
-      <formula>AND(task_start&lt;=I$6,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$6)</formula>
+      <formula>AND(task_start&lt;=I$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$7)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="5" stopIfTrue="1">
-      <formula>AND(task_end&gt;=I$6,task_start&lt;J$6)</formula>
+      <formula>AND(task_end&gt;=I$7,task_start&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I22:AB26">
+  <conditionalFormatting sqref="I39:AB43">
     <cfRule type="expression" dxfId="8" priority="2">
-      <formula>AND(task_start&lt;=I$6,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$6)</formula>
+      <formula>AND(task_start&lt;=I$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$7)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="3" stopIfTrue="1">
-      <formula>AND(task_end&gt;=I$6,task_start&lt;J$6)</formula>
+      <formula>AND(task_end&gt;=I$7,task_start&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC5:AC26">
+  <conditionalFormatting sqref="AC6:AC43">
     <cfRule type="expression" dxfId="6" priority="25">
-      <formula>AND(TODAY()&gt;=AC$6, TODAY()&lt;#REF!)</formula>
+      <formula>AND(TODAY()&gt;=AC$7, TODAY()&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC10:AC14">
+  <conditionalFormatting sqref="AC11:AC17">
     <cfRule type="expression" dxfId="5" priority="28">
-      <formula>AND(task_start&lt;=AC$6,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=AC$6)</formula>
+      <formula>AND(task_start&lt;=AC$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=AC$7)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="29" stopIfTrue="1">
-      <formula>AND(task_end&gt;=AC$6,task_start&lt;#REF!)</formula>
+      <formula>AND(task_end&gt;=AC$7,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC16:AC20">
+  <conditionalFormatting sqref="AC19:AC37">
     <cfRule type="expression" dxfId="3" priority="32">
-      <formula>AND(task_start&lt;=AC$6,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=AC$6)</formula>
+      <formula>AND(task_start&lt;=AC$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=AC$7)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="33" stopIfTrue="1">
-      <formula>AND(task_end&gt;=AC$6,task_start&lt;#REF!)</formula>
+      <formula>AND(task_end&gt;=AC$7,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC22:AC26">
+  <conditionalFormatting sqref="AC39:AC43">
     <cfRule type="expression" dxfId="1" priority="36">
-      <formula>AND(task_start&lt;=AC$6,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=AC$6)</formula>
+      <formula>AND(task_start&lt;=AC$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=AC$7)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="37" stopIfTrue="1">
-      <formula>AND(task_end&gt;=AC$6,task_start&lt;#REF!)</formula>
+      <formula>AND(task_end&gt;=AC$7,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C39:C43 C19:C37" xr:uid="{81BFDE51-3151-43F8-A7A1-718D27BBADDF}">
+      <formula1>$B$2:$B$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11:C17" xr:uid="{57E84E88-ADF7-4240-9B38-62294B230932}">
+      <formula1>$B$2:$B$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="57" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter differentFirst="1" scaleWithDoc="0">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -2710,7 +3532,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D8:D26</xm:sqref>
+          <xm:sqref>D9:D43</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -2719,6 +3541,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3030,36 +3881,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09426A3-87E9-4865-8A6C-3456B026AE03}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3080,33 +3929,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>
--- a/Gantt Chart Cronograma.xlsx
+++ b/Gantt Chart Cronograma.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rayke\Documents\Programacion Web\Programacion 3\Proyecto Final\Reto-3-Grupo-J\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/13b979beda9c5651/Documentos/UASD/Semestre 2026-10/Progamacion 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2B6B4C-5712-4887-B945-2AAA1E2D2CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{10377103-9268-42CD-B802-50DE7F974AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3E080B5-14EF-4676-B6F8-03ED33CA5E86}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="7650" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
     <author>Raykel Villar</author>
   </authors>
   <commentList>
-    <comment ref="B33" authorId="0" shapeId="0" xr:uid="{CB5F8FE0-3A07-4DD7-9A6A-C9EB65374E0F}">
+    <comment ref="B31" authorId="0" shapeId="0" xr:uid="{CB5F8FE0-3A07-4DD7-9A6A-C9EB65374E0F}">
       <text>
         <r>
           <rPr>
@@ -74,7 +74,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B34" authorId="0" shapeId="0" xr:uid="{A3221A40-20FC-434F-8F6B-632DA2F27663}">
+    <comment ref="B32" authorId="0" shapeId="0" xr:uid="{A3221A40-20FC-434F-8F6B-632DA2F27663}">
       <text>
         <r>
           <rPr>
@@ -98,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B35" authorId="0" shapeId="0" xr:uid="{AB31A21F-8F32-4341-99B6-39E3A43DB709}">
+    <comment ref="B33" authorId="0" shapeId="0" xr:uid="{AB31A21F-8F32-4341-99B6-39E3A43DB709}">
       <text>
         <r>
           <rPr>
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="47">
   <si>
     <t xml:space="preserve">Do not delete this row. This row is hidden to preserve a formula that is used to highlight the current day within the project schedule. </t>
   </si>
@@ -222,15 +222,6 @@
     <t>Pagina De Inicio Backend</t>
   </si>
   <si>
-    <t>Pagina De Departamentos HTML</t>
-  </si>
-  <si>
-    <t>Pagina De Departamentos CSS</t>
-  </si>
-  <si>
-    <t>Pagina De Departamentos Backend</t>
-  </si>
-  <si>
     <t>Pagina Lista de Favoritos HTML</t>
   </si>
   <si>
@@ -250,6 +241,33 @@
   </si>
   <si>
     <t>Crear React App</t>
+  </si>
+  <si>
+    <t>Pagina Ordenes HTML</t>
+  </si>
+  <si>
+    <t>Pagina Ordenes CSS</t>
+  </si>
+  <si>
+    <t>Pagina Ordenes Backend</t>
+  </si>
+  <si>
+    <t>Pagina Articulos HTML</t>
+  </si>
+  <si>
+    <t>Pagina Articulos CSS</t>
+  </si>
+  <si>
+    <t>Pagina Articulos Backend</t>
+  </si>
+  <si>
+    <t>Pagina De Departamentos HTML (Opcional)</t>
+  </si>
+  <si>
+    <t>Pagina De Departamentos CSS (Optional)</t>
+  </si>
+  <si>
+    <t>Pagina De Departamentos Backend (Optional)</t>
   </si>
 </sst>
 </file>
@@ -786,7 +804,7 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -967,113 +985,76 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="11" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="12" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -1516,10 +1497,6 @@
 </FeaturePropertyBags>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1726,10 +1703,10 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD46"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="4.58203125" style="6" customWidth="1"/>
     <col min="2" max="2" width="44.33203125" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" customWidth="1"/>
@@ -1740,7 +1717,7 @@
     <col min="9" max="29" width="4.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="90" customHeight="1" x14ac:dyDescent="1.7">
+    <row r="1" spans="1:29" ht="90" customHeight="1" x14ac:dyDescent="1.7">
       <c r="A1" s="7"/>
       <c r="B1" s="66" t="s">
         <v>2</v>
@@ -1750,155 +1727,155 @@
       <c r="E1" s="13"/>
       <c r="F1" s="14"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="77" t="s">
+      <c r="I1" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
       <c r="P1" s="17"/>
-      <c r="Q1" s="75">
+      <c r="Q1" s="81">
         <v>46130</v>
       </c>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-      <c r="V1" s="76"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="76"/>
-      <c r="Y1" s="76"/>
-      <c r="Z1" s="76"/>
-    </row>
-    <row r="2" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="B2" s="85" t="s">
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="82"/>
+      <c r="X1" s="82"/>
+      <c r="Y1" s="82"/>
+      <c r="Z1" s="82"/>
+    </row>
+    <row r="2" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="B2" s="68" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="65"/>
       <c r="D2" s="15"/>
       <c r="E2" s="16"/>
       <c r="F2" s="15"/>
-      <c r="I2" s="79" t="s">
+      <c r="I2" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="86"/>
       <c r="P2" s="67"/>
-      <c r="Q2" s="83">
+      <c r="Q2" s="79">
         <v>2</v>
       </c>
-      <c r="R2" s="84"/>
-      <c r="S2" s="84"/>
-      <c r="T2" s="84"/>
-      <c r="U2" s="84"/>
-      <c r="V2" s="84"/>
-      <c r="W2" s="84"/>
-      <c r="X2" s="84"/>
-      <c r="Y2" s="84"/>
-      <c r="Z2" s="84"/>
-    </row>
-    <row r="3" spans="1:30" s="18" customFormat="1" ht="44.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
+      <c r="Z2" s="80"/>
+    </row>
+    <row r="3" spans="1:29" s="18" customFormat="1" ht="44.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="68" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="20"/>
-      <c r="I3" s="77" t="s">
+      <c r="I3" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="Q3" s="75">
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="84"/>
+      <c r="Q3" s="81">
         <v>46150</v>
       </c>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="W3" s="76"/>
-      <c r="X3" s="76"/>
-      <c r="Y3" s="76"/>
-      <c r="Z3" s="76"/>
-    </row>
-    <row r="4" spans="1:30" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="82"/>
+    </row>
+    <row r="4" spans="1:29" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="68" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:30" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="68" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="20"/>
     </row>
-    <row r="6" spans="1:30" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="21"/>
       <c r="E6" s="22"/>
-      <c r="I6" s="81">
+      <c r="I6" s="75">
         <f>I7</f>
         <v>46130</v>
       </c>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="82"/>
-      <c r="N6" s="82"/>
-      <c r="O6" s="82"/>
-      <c r="P6" s="82">
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="76"/>
+      <c r="O6" s="76"/>
+      <c r="P6" s="76">
         <f>P7</f>
         <v>46137</v>
       </c>
-      <c r="Q6" s="82"/>
-      <c r="R6" s="82"/>
-      <c r="S6" s="82"/>
-      <c r="T6" s="82"/>
-      <c r="U6" s="82"/>
-      <c r="V6" s="82"/>
-      <c r="W6" s="82">
+      <c r="Q6" s="76"/>
+      <c r="R6" s="76"/>
+      <c r="S6" s="76"/>
+      <c r="T6" s="76"/>
+      <c r="U6" s="76"/>
+      <c r="V6" s="76"/>
+      <c r="W6" s="76">
         <f>W7</f>
         <v>46144</v>
       </c>
-      <c r="X6" s="82"/>
-      <c r="Y6" s="82"/>
-      <c r="Z6" s="82"/>
-      <c r="AA6" s="82"/>
-      <c r="AB6" s="82"/>
-      <c r="AC6" s="82"/>
-    </row>
-    <row r="7" spans="1:30" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="69"/>
-      <c r="B7" s="70" t="s">
+      <c r="X6" s="76"/>
+      <c r="Y6" s="76"/>
+      <c r="Z6" s="76"/>
+      <c r="AA6" s="76"/>
+      <c r="AB6" s="76"/>
+      <c r="AC6" s="76"/>
+    </row>
+    <row r="7" spans="1:29" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="87"/>
+      <c r="B7" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="74" t="s">
+      <c r="D7" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="74" t="s">
+      <c r="E7" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="74" t="s">
+      <c r="F7" s="77" t="s">
         <v>6</v>
       </c>
       <c r="I7" s="23">
@@ -1986,13 +1963,13 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="69"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
+    <row r="8" spans="1:29" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="87"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
       <c r="I8" s="26" t="str">
         <f t="shared" ref="I8:AC8" si="1">LEFT(TEXT(I7,"ddd"),1)</f>
         <v>S</v>
@@ -2078,7 +2055,7 @@
         <v>F</v>
       </c>
     </row>
-    <row r="9" spans="1:30" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:29" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>0</v>
       </c>
@@ -2113,7 +2090,7 @@
       <c r="AB9" s="30"/>
       <c r="AC9" s="30"/>
     </row>
-    <row r="10" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="31" t="s">
         <v>10</v>
@@ -2124,7 +2101,7 @@
       <c r="F10" s="35"/>
       <c r="G10" s="10"/>
       <c r="H10" s="5" t="str">
-        <f t="shared" ref="H10:H43" si="2">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f t="shared" ref="H10:H47" si="2">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I10" s="36"/>
@@ -2149,15 +2126,18 @@
       <c r="AB10" s="36"/>
       <c r="AC10" s="36"/>
     </row>
-    <row r="11" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="7"/>
+    <row r="11" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="91" t="b">
+        <v>1</v>
+      </c>
       <c r="B11" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="89" t="s">
+      <c r="C11" s="72" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="39">
+        <f>IF(A11, 100%, 0%)</f>
         <v>1</v>
       </c>
       <c r="E11" s="40">
@@ -2192,20 +2172,20 @@
       <c r="AA11" s="41"/>
       <c r="AB11" s="41"/>
       <c r="AC11" s="41"/>
-      <c r="AD11" s="68" t="b">
+    </row>
+    <row r="12" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="91" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="7"/>
       <c r="B12" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="90" t="s">
+      <c r="C12" s="73" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="43">
-        <v>0.25</v>
+        <f t="shared" ref="D12:D17" si="3">IF(A12, 100%, 0%)</f>
+        <v>0</v>
       </c>
       <c r="E12" s="44">
         <v>46133</v>
@@ -2240,15 +2220,20 @@
       <c r="AB12" s="41"/>
       <c r="AC12" s="41"/>
     </row>
-    <row r="13" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6"/>
+    <row r="13" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="91" t="b">
+        <v>0</v>
+      </c>
       <c r="B13" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="90" t="s">
+      <c r="C13" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="43"/>
+      <c r="D13" s="43">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E13" s="44"/>
       <c r="F13" s="44"/>
       <c r="G13" s="10"/>
@@ -2278,13 +2263,18 @@
       <c r="AB13" s="41"/>
       <c r="AC13" s="41"/>
     </row>
-    <row r="14" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6"/>
+    <row r="14" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="91" t="b">
+        <v>0</v>
+      </c>
       <c r="B14" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="90"/>
-      <c r="D14" s="43"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="43">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E14" s="44">
         <v>46137</v>
       </c>
@@ -2318,13 +2308,18 @@
       <c r="AB14" s="41"/>
       <c r="AC14" s="41"/>
     </row>
-    <row r="15" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6"/>
+    <row r="15" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="91" t="b">
+        <v>0</v>
+      </c>
       <c r="B15" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="90"/>
-      <c r="D15" s="43"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="43">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E15" s="44">
         <v>46137</v>
       </c>
@@ -2358,21 +2353,24 @@
       <c r="AB15" s="41"/>
       <c r="AC15" s="41"/>
     </row>
-    <row r="16" spans="1:30" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="6"/>
-      <c r="B16" s="86" t="s">
+    <row r="16" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="91" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="91" t="s">
+      <c r="C16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="87">
+      <c r="D16" s="70">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E16" s="88">
+      <c r="E16" s="71">
         <v>46137</v>
       </c>
-      <c r="F16" s="103">
+      <c r="F16" s="71">
         <v>46137</v>
       </c>
       <c r="G16" s="10"/>
@@ -2399,46 +2397,49 @@
       <c r="AB16" s="41"/>
       <c r="AC16" s="41"/>
     </row>
-    <row r="17" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="93"/>
-      <c r="B17" s="101" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="104" t="s">
+    <row r="17" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="91" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="102">
+      <c r="D17" s="70">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E17" s="103">
+      <c r="E17" s="71">
         <v>46137</v>
       </c>
-      <c r="F17" s="103">
+      <c r="F17" s="71">
         <v>46137</v>
       </c>
-      <c r="G17" s="94"/>
-      <c r="H17" s="92"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96"/>
-      <c r="M17" s="96"/>
-      <c r="N17" s="96"/>
-      <c r="O17" s="96"/>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
-      <c r="S17" s="96"/>
-      <c r="T17" s="96"/>
-      <c r="U17" s="96"/>
-      <c r="V17" s="96"/>
-      <c r="W17" s="96"/>
-      <c r="X17" s="96"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="96"/>
-      <c r="AA17" s="96"/>
-      <c r="AB17" s="96"/>
-      <c r="AC17" s="96"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="41"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="41"/>
+      <c r="U17" s="41"/>
+      <c r="V17" s="41"/>
+      <c r="W17" s="41"/>
+      <c r="X17" s="41"/>
+      <c r="Y17" s="41"/>
+      <c r="Z17" s="41"/>
+      <c r="AA17" s="41"/>
+      <c r="AB17" s="41"/>
+      <c r="AC17" s="41"/>
     </row>
     <row r="18" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
@@ -2456,8 +2457,10 @@
       </c>
     </row>
     <row r="19" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="7"/>
-      <c r="B19" s="97" t="s">
+      <c r="A19" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B19" s="51" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="52" t="s">
@@ -2498,18 +2501,20 @@
       <c r="AC19" s="41"/>
     </row>
     <row r="20" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="6"/>
-      <c r="B20" s="97" t="s">
+      <c r="A20" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B20" s="51" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="52" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="53"/>
-      <c r="E20" s="100">
+      <c r="E20" s="54">
         <v>46137</v>
       </c>
-      <c r="F20" s="100">
+      <c r="F20" s="54">
         <v>46143</v>
       </c>
       <c r="G20" s="10"/>
@@ -2540,18 +2545,20 @@
       <c r="AC20" s="41"/>
     </row>
     <row r="21" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="6"/>
-      <c r="B21" s="97" t="s">
+      <c r="A21" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B21" s="51" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="52" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="53"/>
-      <c r="E21" s="100">
+      <c r="E21" s="54">
         <v>46137</v>
       </c>
-      <c r="F21" s="100">
+      <c r="F21" s="54">
         <v>46143</v>
       </c>
       <c r="G21" s="10"/>
@@ -2582,25 +2589,24 @@
       <c r="AC21" s="41"/>
     </row>
     <row r="22" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="6"/>
+      <c r="A22" s="91" t="b">
+        <v>0</v>
+      </c>
       <c r="B22" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="98" t="s">
-        <v>13</v>
+        <v>28</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>15</v>
       </c>
       <c r="D22" s="53"/>
-      <c r="E22" s="100">
+      <c r="E22" s="54">
         <v>46137</v>
       </c>
-      <c r="F22" s="100">
+      <c r="F22" s="54">
         <v>46143</v>
       </c>
       <c r="G22" s="10"/>
-      <c r="H22" s="5">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
+      <c r="H22" s="5"/>
       <c r="I22" s="41"/>
       <c r="J22" s="41"/>
       <c r="K22" s="41"/>
@@ -2617,32 +2623,31 @@
       <c r="V22" s="41"/>
       <c r="W22" s="41"/>
       <c r="X22" s="41"/>
-      <c r="Y22" s="45"/>
+      <c r="Y22" s="41"/>
       <c r="Z22" s="41"/>
       <c r="AA22" s="41"/>
       <c r="AB22" s="41"/>
       <c r="AC22" s="41"/>
     </row>
     <row r="23" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="6"/>
+      <c r="A23" s="91" t="b">
+        <v>0</v>
+      </c>
       <c r="B23" s="51" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" s="53"/>
-      <c r="E23" s="100">
+      <c r="E23" s="54">
         <v>46137</v>
       </c>
-      <c r="F23" s="100">
+      <c r="F23" s="54">
         <v>46143</v>
       </c>
       <c r="G23" s="10"/>
-      <c r="H23" s="5">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
+      <c r="H23" s="5"/>
       <c r="I23" s="41"/>
       <c r="J23" s="41"/>
       <c r="K23" s="41"/>
@@ -2665,584 +2670,640 @@
       <c r="AB23" s="41"/>
       <c r="AC23" s="41"/>
     </row>
-    <row r="24" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="93"/>
-      <c r="B24" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="98" t="s">
+    <row r="24" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B24" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="53"/>
+      <c r="E24" s="54">
+        <v>46137</v>
+      </c>
+      <c r="F24" s="54">
+        <v>46143</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="41"/>
+      <c r="M24" s="41"/>
+      <c r="N24" s="41"/>
+      <c r="O24" s="41"/>
+      <c r="P24" s="41"/>
+      <c r="Q24" s="41"/>
+      <c r="R24" s="41"/>
+      <c r="S24" s="41"/>
+      <c r="T24" s="41"/>
+      <c r="U24" s="41"/>
+      <c r="V24" s="41"/>
+      <c r="W24" s="41"/>
+      <c r="X24" s="41"/>
+      <c r="Y24" s="41"/>
+      <c r="Z24" s="41"/>
+      <c r="AA24" s="41"/>
+      <c r="AB24" s="41"/>
+      <c r="AC24" s="41"/>
+    </row>
+    <row r="25" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="99"/>
-      <c r="E24" s="100">
+      <c r="D25" s="53"/>
+      <c r="E25" s="54">
         <v>46137</v>
       </c>
-      <c r="F24" s="100">
+      <c r="F25" s="54">
         <v>46143</v>
       </c>
-      <c r="G24" s="94"/>
-      <c r="H24" s="92"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="96"/>
-      <c r="K24" s="96"/>
-      <c r="L24" s="96"/>
-      <c r="M24" s="96"/>
-      <c r="N24" s="96"/>
-      <c r="O24" s="96"/>
-      <c r="P24" s="96"/>
-      <c r="Q24" s="96"/>
-      <c r="R24" s="96"/>
-      <c r="S24" s="96"/>
-      <c r="T24" s="96"/>
-      <c r="U24" s="96"/>
-      <c r="V24" s="96"/>
-      <c r="W24" s="96"/>
-      <c r="X24" s="96"/>
-      <c r="Y24" s="96"/>
-      <c r="Z24" s="96"/>
-      <c r="AA24" s="96"/>
-      <c r="AB24" s="96"/>
-      <c r="AC24" s="96"/>
-    </row>
-    <row r="25" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="93"/>
-      <c r="B25" s="97" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="98" t="s">
+      <c r="G25" s="10"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="41"/>
+      <c r="R25" s="41"/>
+      <c r="S25" s="41"/>
+      <c r="T25" s="41"/>
+      <c r="U25" s="41"/>
+      <c r="V25" s="41"/>
+      <c r="W25" s="41"/>
+      <c r="X25" s="41"/>
+      <c r="Y25" s="41"/>
+      <c r="Z25" s="41"/>
+      <c r="AA25" s="41"/>
+      <c r="AB25" s="41"/>
+      <c r="AC25" s="41"/>
+    </row>
+    <row r="26" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="99"/>
-      <c r="E25" s="100">
+      <c r="D26" s="53"/>
+      <c r="E26" s="54">
         <v>46137</v>
       </c>
-      <c r="F25" s="100">
+      <c r="F26" s="54">
         <v>46143</v>
       </c>
-      <c r="G25" s="94"/>
-      <c r="H25" s="92"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="96"/>
-      <c r="K25" s="96"/>
-      <c r="L25" s="96"/>
-      <c r="M25" s="96"/>
-      <c r="N25" s="96"/>
-      <c r="O25" s="96"/>
-      <c r="P25" s="96"/>
-      <c r="Q25" s="96"/>
-      <c r="R25" s="96"/>
-      <c r="S25" s="96"/>
-      <c r="T25" s="96"/>
-      <c r="U25" s="96"/>
-      <c r="V25" s="96"/>
-      <c r="W25" s="96"/>
-      <c r="X25" s="96"/>
-      <c r="Y25" s="96"/>
-      <c r="Z25" s="96"/>
-      <c r="AA25" s="96"/>
-      <c r="AB25" s="96"/>
-      <c r="AC25" s="96"/>
-    </row>
-    <row r="26" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="93"/>
-      <c r="B26" s="97" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="98" t="s">
+      <c r="G26" s="10"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="41"/>
+      <c r="R26" s="41"/>
+      <c r="S26" s="41"/>
+      <c r="T26" s="41"/>
+      <c r="U26" s="41"/>
+      <c r="V26" s="41"/>
+      <c r="W26" s="41"/>
+      <c r="X26" s="41"/>
+      <c r="Y26" s="41"/>
+      <c r="Z26" s="41"/>
+      <c r="AA26" s="41"/>
+      <c r="AB26" s="41"/>
+      <c r="AC26" s="41"/>
+    </row>
+    <row r="27" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B27" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="99"/>
-      <c r="E26" s="100">
+      <c r="D27" s="53"/>
+      <c r="E27" s="54">
         <v>46137</v>
       </c>
-      <c r="F26" s="100">
+      <c r="F27" s="54">
         <v>46143</v>
       </c>
-      <c r="G26" s="94"/>
-      <c r="H26" s="92"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="96"/>
-      <c r="K26" s="96"/>
-      <c r="L26" s="96"/>
-      <c r="M26" s="96"/>
-      <c r="N26" s="96"/>
-      <c r="O26" s="96"/>
-      <c r="P26" s="96"/>
-      <c r="Q26" s="96"/>
-      <c r="R26" s="96"/>
-      <c r="S26" s="96"/>
-      <c r="T26" s="96"/>
-      <c r="U26" s="96"/>
-      <c r="V26" s="96"/>
-      <c r="W26" s="96"/>
-      <c r="X26" s="96"/>
-      <c r="Y26" s="96"/>
-      <c r="Z26" s="96"/>
-      <c r="AA26" s="96"/>
-      <c r="AB26" s="96"/>
-      <c r="AC26" s="96"/>
-    </row>
-    <row r="27" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="93"/>
-      <c r="B27" s="97" t="s">
+      <c r="G27" s="10"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="41"/>
+      <c r="S27" s="41"/>
+      <c r="T27" s="41"/>
+      <c r="U27" s="41"/>
+      <c r="V27" s="41"/>
+      <c r="W27" s="41"/>
+      <c r="X27" s="41"/>
+      <c r="Y27" s="41"/>
+      <c r="Z27" s="41"/>
+      <c r="AA27" s="41"/>
+      <c r="AB27" s="41"/>
+      <c r="AC27" s="41"/>
+    </row>
+    <row r="28" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B28" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="98" t="s">
+      <c r="C28" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="99"/>
-      <c r="E27" s="100">
+      <c r="D28" s="53"/>
+      <c r="E28" s="54">
         <v>46137</v>
       </c>
-      <c r="F27" s="100">
+      <c r="F28" s="54">
         <v>46143</v>
       </c>
-      <c r="G27" s="94"/>
-      <c r="H27" s="92"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="96"/>
-      <c r="K27" s="96"/>
-      <c r="L27" s="96"/>
-      <c r="M27" s="96"/>
-      <c r="N27" s="96"/>
-      <c r="O27" s="96"/>
-      <c r="P27" s="96"/>
-      <c r="Q27" s="96"/>
-      <c r="R27" s="96"/>
-      <c r="S27" s="96"/>
-      <c r="T27" s="96"/>
-      <c r="U27" s="96"/>
-      <c r="V27" s="96"/>
-      <c r="W27" s="96"/>
-      <c r="X27" s="96"/>
-      <c r="Y27" s="96"/>
-      <c r="Z27" s="96"/>
-      <c r="AA27" s="96"/>
-      <c r="AB27" s="96"/>
-      <c r="AC27" s="96"/>
-    </row>
-    <row r="28" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="93"/>
-      <c r="B28" s="97" t="s">
+      <c r="G28" s="10"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="41"/>
+      <c r="S28" s="41"/>
+      <c r="T28" s="41"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="41"/>
+      <c r="W28" s="41"/>
+      <c r="X28" s="41"/>
+      <c r="Y28" s="41"/>
+      <c r="Z28" s="41"/>
+      <c r="AA28" s="41"/>
+      <c r="AB28" s="41"/>
+      <c r="AC28" s="41"/>
+    </row>
+    <row r="29" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B29" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="98" t="s">
+      <c r="C29" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="99"/>
-      <c r="E28" s="100">
+      <c r="D29" s="53"/>
+      <c r="E29" s="54">
         <v>46137</v>
       </c>
-      <c r="F28" s="100">
+      <c r="F29" s="54">
         <v>46143</v>
       </c>
-      <c r="G28" s="94"/>
-      <c r="H28" s="92"/>
-      <c r="I28" s="96"/>
-      <c r="J28" s="96"/>
-      <c r="K28" s="96"/>
-      <c r="L28" s="96"/>
-      <c r="M28" s="96"/>
-      <c r="N28" s="96"/>
-      <c r="O28" s="96"/>
-      <c r="P28" s="96"/>
-      <c r="Q28" s="96"/>
-      <c r="R28" s="96"/>
-      <c r="S28" s="96"/>
-      <c r="T28" s="96"/>
-      <c r="U28" s="96"/>
-      <c r="V28" s="96"/>
-      <c r="W28" s="96"/>
-      <c r="X28" s="96"/>
-      <c r="Y28" s="96"/>
-      <c r="Z28" s="96"/>
-      <c r="AA28" s="96"/>
-      <c r="AB28" s="96"/>
-      <c r="AC28" s="96"/>
-    </row>
-    <row r="29" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="93"/>
-      <c r="B29" s="97" t="s">
+      <c r="G29" s="10"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="41"/>
+      <c r="S29" s="41"/>
+      <c r="T29" s="41"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="41"/>
+      <c r="W29" s="41"/>
+      <c r="X29" s="41"/>
+      <c r="Y29" s="41"/>
+      <c r="Z29" s="41"/>
+      <c r="AA29" s="41"/>
+      <c r="AB29" s="41"/>
+      <c r="AC29" s="41"/>
+    </row>
+    <row r="30" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B30" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="98" t="s">
+      <c r="C30" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="99"/>
-      <c r="E29" s="100">
+      <c r="D30" s="53"/>
+      <c r="E30" s="54">
         <v>46137</v>
       </c>
-      <c r="F29" s="100">
+      <c r="F30" s="54">
         <v>46143</v>
       </c>
-      <c r="G29" s="94"/>
-      <c r="H29" s="92"/>
-      <c r="I29" s="96"/>
-      <c r="J29" s="96"/>
-      <c r="K29" s="96"/>
-      <c r="L29" s="96"/>
-      <c r="M29" s="96"/>
-      <c r="N29" s="96"/>
-      <c r="O29" s="96"/>
-      <c r="P29" s="96"/>
-      <c r="Q29" s="96"/>
-      <c r="R29" s="96"/>
-      <c r="S29" s="96"/>
-      <c r="T29" s="96"/>
-      <c r="U29" s="96"/>
-      <c r="V29" s="96"/>
-      <c r="W29" s="96"/>
-      <c r="X29" s="96"/>
-      <c r="Y29" s="96"/>
-      <c r="Z29" s="96"/>
-      <c r="AA29" s="96"/>
-      <c r="AB29" s="96"/>
-      <c r="AC29" s="96"/>
-    </row>
-    <row r="30" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="93"/>
-      <c r="B30" s="97" t="s">
+      <c r="G30" s="10"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="41"/>
+      <c r="S30" s="41"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="41"/>
+      <c r="W30" s="41"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="41"/>
+      <c r="Z30" s="41"/>
+      <c r="AA30" s="41"/>
+      <c r="AB30" s="41"/>
+      <c r="AC30" s="41"/>
+    </row>
+    <row r="31" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B31" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="98" t="s">
+      <c r="C31" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="99"/>
-      <c r="E30" s="100">
+      <c r="D31" s="53"/>
+      <c r="E31" s="54">
         <v>46137</v>
       </c>
-      <c r="F30" s="100">
+      <c r="F31" s="54">
         <v>46143</v>
       </c>
-      <c r="G30" s="94"/>
-      <c r="H30" s="92"/>
-      <c r="I30" s="96"/>
-      <c r="J30" s="96"/>
-      <c r="K30" s="96"/>
-      <c r="L30" s="96"/>
-      <c r="M30" s="96"/>
-      <c r="N30" s="96"/>
-      <c r="O30" s="96"/>
-      <c r="P30" s="96"/>
-      <c r="Q30" s="96"/>
-      <c r="R30" s="96"/>
-      <c r="S30" s="96"/>
-      <c r="T30" s="96"/>
-      <c r="U30" s="96"/>
-      <c r="V30" s="96"/>
-      <c r="W30" s="96"/>
-      <c r="X30" s="96"/>
-      <c r="Y30" s="96"/>
-      <c r="Z30" s="96"/>
-      <c r="AA30" s="96"/>
-      <c r="AB30" s="96"/>
-      <c r="AC30" s="96"/>
-    </row>
-    <row r="31" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="93"/>
-      <c r="B31" s="97" t="s">
+      <c r="G31" s="10"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="41"/>
+      <c r="S31" s="41"/>
+      <c r="T31" s="41"/>
+      <c r="U31" s="41"/>
+      <c r="V31" s="41"/>
+      <c r="W31" s="41"/>
+      <c r="X31" s="41"/>
+      <c r="Y31" s="41"/>
+      <c r="Z31" s="41"/>
+      <c r="AA31" s="41"/>
+      <c r="AB31" s="41"/>
+      <c r="AC31" s="41"/>
+    </row>
+    <row r="32" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B32" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="98" t="s">
+      <c r="C32" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="99"/>
-      <c r="E31" s="100">
+      <c r="D32" s="53"/>
+      <c r="E32" s="54">
         <v>46137</v>
       </c>
-      <c r="F31" s="100">
+      <c r="F32" s="54">
         <v>46143</v>
       </c>
-      <c r="G31" s="94"/>
-      <c r="H31" s="92"/>
-      <c r="I31" s="96"/>
-      <c r="J31" s="96"/>
-      <c r="K31" s="96"/>
-      <c r="L31" s="96"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="96"/>
-      <c r="O31" s="96"/>
-      <c r="P31" s="96"/>
-      <c r="Q31" s="96"/>
-      <c r="R31" s="96"/>
-      <c r="S31" s="96"/>
-      <c r="T31" s="96"/>
-      <c r="U31" s="96"/>
-      <c r="V31" s="96"/>
-      <c r="W31" s="96"/>
-      <c r="X31" s="96"/>
-      <c r="Y31" s="96"/>
-      <c r="Z31" s="96"/>
-      <c r="AA31" s="96"/>
-      <c r="AB31" s="96"/>
-      <c r="AC31" s="96"/>
-    </row>
-    <row r="32" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="93"/>
-      <c r="B32" s="97" t="s">
+      <c r="G32" s="10"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="41"/>
+      <c r="M32" s="41"/>
+      <c r="N32" s="41"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="41"/>
+      <c r="S32" s="41"/>
+      <c r="T32" s="41"/>
+      <c r="U32" s="41"/>
+      <c r="V32" s="41"/>
+      <c r="W32" s="41"/>
+      <c r="X32" s="41"/>
+      <c r="Y32" s="41"/>
+      <c r="Z32" s="41"/>
+      <c r="AA32" s="41"/>
+      <c r="AB32" s="41"/>
+      <c r="AC32" s="41"/>
+    </row>
+    <row r="33" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B33" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="98" t="s">
+      <c r="C33" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="99"/>
-      <c r="E32" s="100">
+      <c r="D33" s="53"/>
+      <c r="E33" s="54">
         <v>46137</v>
       </c>
-      <c r="F32" s="100">
+      <c r="F33" s="54">
         <v>46143</v>
       </c>
-      <c r="G32" s="94"/>
-      <c r="H32" s="92"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="96"/>
-      <c r="K32" s="96"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="96"/>
-      <c r="N32" s="96"/>
-      <c r="O32" s="96"/>
-      <c r="P32" s="96"/>
-      <c r="Q32" s="96"/>
-      <c r="R32" s="96"/>
-      <c r="S32" s="96"/>
-      <c r="T32" s="96"/>
-      <c r="U32" s="96"/>
-      <c r="V32" s="96"/>
-      <c r="W32" s="96"/>
-      <c r="X32" s="96"/>
-      <c r="Y32" s="96"/>
-      <c r="Z32" s="96"/>
-      <c r="AA32" s="96"/>
-      <c r="AB32" s="96"/>
-      <c r="AC32" s="96"/>
-    </row>
-    <row r="33" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="93"/>
-      <c r="B33" s="97" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="98" t="s">
+      <c r="G33" s="10"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="41"/>
+      <c r="S33" s="41"/>
+      <c r="T33" s="41"/>
+      <c r="U33" s="41"/>
+      <c r="V33" s="41"/>
+      <c r="W33" s="41"/>
+      <c r="X33" s="41"/>
+      <c r="Y33" s="41"/>
+      <c r="Z33" s="41"/>
+      <c r="AA33" s="41"/>
+      <c r="AB33" s="41"/>
+      <c r="AC33" s="41"/>
+    </row>
+    <row r="34" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B34" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="99"/>
-      <c r="E33" s="100">
+      <c r="D34" s="53"/>
+      <c r="E34" s="54">
         <v>46137</v>
       </c>
-      <c r="F33" s="100">
+      <c r="F34" s="54">
         <v>46143</v>
       </c>
-      <c r="G33" s="94"/>
-      <c r="H33" s="92"/>
-      <c r="I33" s="96"/>
-      <c r="J33" s="96"/>
-      <c r="K33" s="96"/>
-      <c r="L33" s="96"/>
-      <c r="M33" s="96"/>
-      <c r="N33" s="96"/>
-      <c r="O33" s="96"/>
-      <c r="P33" s="96"/>
-      <c r="Q33" s="96"/>
-      <c r="R33" s="96"/>
-      <c r="S33" s="96"/>
-      <c r="T33" s="96"/>
-      <c r="U33" s="96"/>
-      <c r="V33" s="96"/>
-      <c r="W33" s="96"/>
-      <c r="X33" s="96"/>
-      <c r="Y33" s="96"/>
-      <c r="Z33" s="96"/>
-      <c r="AA33" s="96"/>
-      <c r="AB33" s="96"/>
-      <c r="AC33" s="96"/>
-    </row>
-    <row r="34" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="93"/>
-      <c r="B34" s="97" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="98" t="s">
+      <c r="G34" s="10"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="41"/>
+      <c r="N34" s="41"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="41"/>
+      <c r="S34" s="41"/>
+      <c r="T34" s="41"/>
+      <c r="U34" s="41"/>
+      <c r="V34" s="41"/>
+      <c r="W34" s="41"/>
+      <c r="X34" s="41"/>
+      <c r="Y34" s="41"/>
+      <c r="Z34" s="41"/>
+      <c r="AA34" s="41"/>
+      <c r="AB34" s="41"/>
+      <c r="AC34" s="41"/>
+    </row>
+    <row r="35" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B35" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="99"/>
-      <c r="E34" s="100">
+      <c r="D35" s="53"/>
+      <c r="E35" s="54">
         <v>46137</v>
       </c>
-      <c r="F34" s="100">
+      <c r="F35" s="54">
         <v>46143</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="96"/>
-      <c r="J34" s="96"/>
-      <c r="K34" s="96"/>
-      <c r="L34" s="96"/>
-      <c r="M34" s="96"/>
-      <c r="N34" s="96"/>
-      <c r="O34" s="96"/>
-      <c r="P34" s="96"/>
-      <c r="Q34" s="96"/>
-      <c r="R34" s="96"/>
-      <c r="S34" s="96"/>
-      <c r="T34" s="96"/>
-      <c r="U34" s="96"/>
-      <c r="V34" s="96"/>
-      <c r="W34" s="96"/>
-      <c r="X34" s="96"/>
-      <c r="Y34" s="96"/>
-      <c r="Z34" s="96"/>
-      <c r="AA34" s="96"/>
-      <c r="AB34" s="96"/>
-      <c r="AC34" s="96"/>
-    </row>
-    <row r="35" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="93"/>
-      <c r="B35" s="97" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="98" t="s">
+      <c r="G35" s="10"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="41"/>
+      <c r="M35" s="41"/>
+      <c r="N35" s="41"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="41"/>
+      <c r="S35" s="41"/>
+      <c r="T35" s="41"/>
+      <c r="U35" s="41"/>
+      <c r="V35" s="41"/>
+      <c r="W35" s="41"/>
+      <c r="X35" s="41"/>
+      <c r="Y35" s="41"/>
+      <c r="Z35" s="41"/>
+      <c r="AA35" s="41"/>
+      <c r="AB35" s="41"/>
+      <c r="AC35" s="41"/>
+    </row>
+    <row r="36" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B36" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="99"/>
-      <c r="E35" s="100">
+      <c r="D36" s="53"/>
+      <c r="E36" s="54">
         <v>46137</v>
       </c>
-      <c r="F35" s="100">
+      <c r="F36" s="54">
         <v>46143</v>
       </c>
-      <c r="G35" s="94"/>
-      <c r="H35" s="92"/>
-      <c r="I35" s="96"/>
-      <c r="J35" s="96"/>
-      <c r="K35" s="96"/>
-      <c r="L35" s="96"/>
-      <c r="M35" s="96"/>
-      <c r="N35" s="96"/>
-      <c r="O35" s="96"/>
-      <c r="P35" s="96"/>
-      <c r="Q35" s="96"/>
-      <c r="R35" s="96"/>
-      <c r="S35" s="96"/>
-      <c r="T35" s="96"/>
-      <c r="U35" s="96"/>
-      <c r="V35" s="96"/>
-      <c r="W35" s="96"/>
-      <c r="X35" s="96"/>
-      <c r="Y35" s="96"/>
-      <c r="Z35" s="96"/>
-      <c r="AA35" s="96"/>
-      <c r="AB35" s="96"/>
-      <c r="AC35" s="96"/>
-    </row>
-    <row r="36" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="93"/>
-      <c r="B36" s="97"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="99"/>
-      <c r="E36" s="100"/>
-      <c r="F36" s="100"/>
-      <c r="G36" s="94"/>
-      <c r="H36" s="92"/>
-      <c r="I36" s="96"/>
-      <c r="J36" s="96"/>
-      <c r="K36" s="96"/>
-      <c r="L36" s="96"/>
-      <c r="M36" s="96"/>
-      <c r="N36" s="96"/>
-      <c r="O36" s="96"/>
-      <c r="P36" s="96"/>
-      <c r="Q36" s="96"/>
-      <c r="R36" s="96"/>
-      <c r="S36" s="96"/>
-      <c r="T36" s="96"/>
-      <c r="U36" s="96"/>
-      <c r="V36" s="96"/>
-      <c r="W36" s="96"/>
-      <c r="X36" s="96"/>
-      <c r="Y36" s="96"/>
-      <c r="Z36" s="96"/>
-      <c r="AA36" s="96"/>
-      <c r="AB36" s="96"/>
-      <c r="AC36" s="96"/>
-    </row>
-    <row r="37" spans="1:29" s="95" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="93"/>
-      <c r="B37" s="97"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="99"/>
-      <c r="E37" s="100"/>
-      <c r="F37" s="100"/>
-      <c r="G37" s="94"/>
-      <c r="H37" s="92"/>
-      <c r="I37" s="96"/>
-      <c r="J37" s="96"/>
-      <c r="K37" s="96"/>
-      <c r="L37" s="96"/>
-      <c r="M37" s="96"/>
-      <c r="N37" s="96"/>
-      <c r="O37" s="96"/>
-      <c r="P37" s="96"/>
-      <c r="Q37" s="96"/>
-      <c r="R37" s="96"/>
-      <c r="S37" s="96"/>
-      <c r="T37" s="96"/>
-      <c r="U37" s="96"/>
-      <c r="V37" s="96"/>
-      <c r="W37" s="96"/>
-      <c r="X37" s="96"/>
-      <c r="Y37" s="96"/>
-      <c r="Z37" s="96"/>
-      <c r="AA37" s="96"/>
-      <c r="AB37" s="96"/>
-      <c r="AC37" s="96"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="41"/>
+      <c r="K36" s="41"/>
+      <c r="L36" s="41"/>
+      <c r="M36" s="41"/>
+      <c r="N36" s="41"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="41"/>
+      <c r="S36" s="41"/>
+      <c r="T36" s="41"/>
+      <c r="U36" s="41"/>
+      <c r="V36" s="41"/>
+      <c r="W36" s="41"/>
+      <c r="X36" s="41"/>
+      <c r="Y36" s="41"/>
+      <c r="Z36" s="41"/>
+      <c r="AA36" s="41"/>
+      <c r="AB36" s="41"/>
+      <c r="AC36" s="41"/>
+    </row>
+    <row r="37" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B37" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="53"/>
+      <c r="E37" s="54">
+        <v>46137</v>
+      </c>
+      <c r="F37" s="54">
+        <v>46143</v>
+      </c>
+      <c r="G37" s="10"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="41"/>
+      <c r="K37" s="41"/>
+      <c r="L37" s="41"/>
+      <c r="M37" s="41"/>
+      <c r="N37" s="41"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="41"/>
+      <c r="S37" s="41"/>
+      <c r="T37" s="41"/>
+      <c r="U37" s="41"/>
+      <c r="V37" s="41"/>
+      <c r="W37" s="41"/>
+      <c r="X37" s="41"/>
+      <c r="Y37" s="41"/>
+      <c r="Z37" s="41"/>
+      <c r="AA37" s="41"/>
+      <c r="AB37" s="41"/>
+      <c r="AC37" s="41"/>
     </row>
     <row r="38" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="6"/>
-      <c r="B38" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="56"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="59"/>
+      <c r="A38" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B38" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="53"/>
+      <c r="E38" s="54">
+        <v>46137</v>
+      </c>
+      <c r="F38" s="54">
+        <v>46143</v>
+      </c>
       <c r="G38" s="10"/>
-      <c r="H38" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="I38" s="60"/>
-      <c r="J38" s="60"/>
-      <c r="K38" s="60"/>
-      <c r="L38" s="60"/>
-      <c r="M38" s="60"/>
-      <c r="N38" s="60"/>
-      <c r="O38" s="60"/>
-      <c r="P38" s="60"/>
-      <c r="Q38" s="60"/>
-      <c r="R38" s="60"/>
-      <c r="S38" s="60"/>
-      <c r="T38" s="60"/>
-      <c r="U38" s="60"/>
-      <c r="V38" s="60"/>
-      <c r="W38" s="60"/>
-      <c r="X38" s="60"/>
-      <c r="Y38" s="60"/>
-      <c r="Z38" s="60"/>
-      <c r="AA38" s="60"/>
-      <c r="AB38" s="60"/>
-      <c r="AC38" s="60"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="41"/>
+      <c r="K38" s="41"/>
+      <c r="L38" s="41"/>
+      <c r="M38" s="41"/>
+      <c r="N38" s="41"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="41"/>
+      <c r="S38" s="41"/>
+      <c r="T38" s="41"/>
+      <c r="U38" s="41"/>
+      <c r="V38" s="41"/>
+      <c r="W38" s="41"/>
+      <c r="X38" s="41"/>
+      <c r="Y38" s="41"/>
+      <c r="Z38" s="41"/>
+      <c r="AA38" s="41"/>
+      <c r="AB38" s="41"/>
+      <c r="AC38" s="41"/>
     </row>
     <row r="39" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="6"/>
-      <c r="B39" s="61"/>
-      <c r="C39" s="62"/>
-      <c r="D39" s="63"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="64"/>
+      <c r="A39" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="53"/>
+      <c r="E39" s="54">
+        <v>46137</v>
+      </c>
+      <c r="F39" s="54">
+        <v>46143</v>
+      </c>
       <c r="G39" s="10"/>
-      <c r="H39" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="H39" s="5"/>
       <c r="I39" s="41"/>
       <c r="J39" s="41"/>
       <c r="K39" s="41"/>
@@ -3266,16 +3327,26 @@
       <c r="AC39" s="41"/>
     </row>
     <row r="40" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="6"/>
-      <c r="B40" s="61"/>
-      <c r="C40" s="62"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
+      <c r="A40" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B40" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="53"/>
+      <c r="E40" s="54">
+        <v>46137</v>
+      </c>
+      <c r="F40" s="54">
+        <v>46143</v>
+      </c>
       <c r="G40" s="10"/>
-      <c r="H40" s="5" t="str">
+      <c r="H40" s="5">
         <f t="shared" si="2"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I40" s="41"/>
       <c r="J40" s="41"/>
@@ -3293,23 +3364,33 @@
       <c r="V40" s="41"/>
       <c r="W40" s="41"/>
       <c r="X40" s="41"/>
-      <c r="Y40" s="41"/>
+      <c r="Y40" s="45"/>
       <c r="Z40" s="41"/>
       <c r="AA40" s="41"/>
       <c r="AB40" s="41"/>
       <c r="AC40" s="41"/>
     </row>
     <row r="41" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="6"/>
-      <c r="B41" s="61"/>
-      <c r="C41" s="62"/>
-      <c r="D41" s="63"/>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64"/>
+      <c r="A41" s="91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B41" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="53"/>
+      <c r="E41" s="54">
+        <v>46137</v>
+      </c>
+      <c r="F41" s="54">
+        <v>46143</v>
+      </c>
       <c r="G41" s="10"/>
-      <c r="H41" s="5" t="str">
+      <c r="H41" s="5">
         <f t="shared" si="2"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I41" s="41"/>
       <c r="J41" s="41"/>
@@ -3335,37 +3416,39 @@
     </row>
     <row r="42" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6"/>
-      <c r="B42" s="61"/>
-      <c r="C42" s="62"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
+      <c r="B42" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="56"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="59"/>
       <c r="G42" s="10"/>
       <c r="H42" s="5" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I42" s="41"/>
-      <c r="J42" s="41"/>
-      <c r="K42" s="41"/>
-      <c r="L42" s="41"/>
-      <c r="M42" s="41"/>
-      <c r="N42" s="41"/>
-      <c r="O42" s="41"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="41"/>
-      <c r="S42" s="41"/>
-      <c r="T42" s="41"/>
-      <c r="U42" s="41"/>
-      <c r="V42" s="41"/>
-      <c r="W42" s="41"/>
-      <c r="X42" s="41"/>
-      <c r="Y42" s="41"/>
-      <c r="Z42" s="41"/>
-      <c r="AA42" s="41"/>
-      <c r="AB42" s="41"/>
-      <c r="AC42" s="41"/>
+      <c r="I42" s="60"/>
+      <c r="J42" s="60"/>
+      <c r="K42" s="60"/>
+      <c r="L42" s="60"/>
+      <c r="M42" s="60"/>
+      <c r="N42" s="60"/>
+      <c r="O42" s="60"/>
+      <c r="P42" s="60"/>
+      <c r="Q42" s="60"/>
+      <c r="R42" s="60"/>
+      <c r="S42" s="60"/>
+      <c r="T42" s="60"/>
+      <c r="U42" s="60"/>
+      <c r="V42" s="60"/>
+      <c r="W42" s="60"/>
+      <c r="X42" s="60"/>
+      <c r="Y42" s="60"/>
+      <c r="Z42" s="60"/>
+      <c r="AA42" s="60"/>
+      <c r="AB42" s="60"/>
+      <c r="AC42" s="60"/>
     </row>
     <row r="43" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6"/>
@@ -3401,35 +3484,171 @@
       <c r="AB43" s="41"/>
       <c r="AC43" s="41"/>
     </row>
-    <row r="44" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G44" s="3"/>
-    </row>
-    <row r="45" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="9"/>
-      <c r="F45" s="8"/>
-    </row>
-    <row r="46" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="4"/>
+    <row r="44" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="6"/>
+      <c r="B44" s="61"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="64"/>
+      <c r="F44" s="64"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="I44" s="41"/>
+      <c r="J44" s="41"/>
+      <c r="K44" s="41"/>
+      <c r="L44" s="41"/>
+      <c r="M44" s="41"/>
+      <c r="N44" s="41"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="41"/>
+      <c r="S44" s="41"/>
+      <c r="T44" s="41"/>
+      <c r="U44" s="41"/>
+      <c r="V44" s="41"/>
+      <c r="W44" s="41"/>
+      <c r="X44" s="41"/>
+      <c r="Y44" s="41"/>
+      <c r="Z44" s="41"/>
+      <c r="AA44" s="41"/>
+      <c r="AB44" s="41"/>
+      <c r="AC44" s="41"/>
+    </row>
+    <row r="45" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="6"/>
+      <c r="B45" s="61"/>
+      <c r="C45" s="62"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="64"/>
+      <c r="F45" s="64"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="I45" s="41"/>
+      <c r="J45" s="41"/>
+      <c r="K45" s="41"/>
+      <c r="L45" s="41"/>
+      <c r="M45" s="41"/>
+      <c r="N45" s="41"/>
+      <c r="O45" s="41"/>
+      <c r="P45" s="41"/>
+      <c r="Q45" s="41"/>
+      <c r="R45" s="41"/>
+      <c r="S45" s="41"/>
+      <c r="T45" s="41"/>
+      <c r="U45" s="41"/>
+      <c r="V45" s="41"/>
+      <c r="W45" s="41"/>
+      <c r="X45" s="41"/>
+      <c r="Y45" s="41"/>
+      <c r="Z45" s="41"/>
+      <c r="AA45" s="41"/>
+      <c r="AB45" s="41"/>
+      <c r="AC45" s="41"/>
+    </row>
+    <row r="46" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="6"/>
+      <c r="B46" s="61"/>
+      <c r="C46" s="62"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="I46" s="41"/>
+      <c r="J46" s="41"/>
+      <c r="K46" s="41"/>
+      <c r="L46" s="41"/>
+      <c r="M46" s="41"/>
+      <c r="N46" s="41"/>
+      <c r="O46" s="41"/>
+      <c r="P46" s="41"/>
+      <c r="Q46" s="41"/>
+      <c r="R46" s="41"/>
+      <c r="S46" s="41"/>
+      <c r="T46" s="41"/>
+      <c r="U46" s="41"/>
+      <c r="V46" s="41"/>
+      <c r="W46" s="41"/>
+      <c r="X46" s="41"/>
+      <c r="Y46" s="41"/>
+      <c r="Z46" s="41"/>
+      <c r="AA46" s="41"/>
+      <c r="AB46" s="41"/>
+      <c r="AC46" s="41"/>
+    </row>
+    <row r="47" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="6"/>
+      <c r="B47" s="61"/>
+      <c r="C47" s="62"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="64"/>
+      <c r="F47" s="64"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="I47" s="41"/>
+      <c r="J47" s="41"/>
+      <c r="K47" s="41"/>
+      <c r="L47" s="41"/>
+      <c r="M47" s="41"/>
+      <c r="N47" s="41"/>
+      <c r="O47" s="41"/>
+      <c r="P47" s="41"/>
+      <c r="Q47" s="41"/>
+      <c r="R47" s="41"/>
+      <c r="S47" s="41"/>
+      <c r="T47" s="41"/>
+      <c r="U47" s="41"/>
+      <c r="V47" s="41"/>
+      <c r="W47" s="41"/>
+      <c r="X47" s="41"/>
+      <c r="Y47" s="41"/>
+      <c r="Z47" s="41"/>
+      <c r="AA47" s="41"/>
+      <c r="AB47" s="41"/>
+      <c r="AC47" s="41"/>
+    </row>
+    <row r="48" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G48" s="3"/>
+    </row>
+    <row r="49" spans="3:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="9"/>
+      <c r="F49" s="8"/>
+    </row>
+    <row r="50" spans="3:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C50" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="Q1:Z1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="I3:O3"/>
+    <mergeCell ref="Q3:Z3"/>
     <mergeCell ref="I6:O6"/>
     <mergeCell ref="P6:V6"/>
     <mergeCell ref="W6:AC6"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="Q1:Z1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:O2"/>
-    <mergeCell ref="I3:O3"/>
-    <mergeCell ref="Q3:Z3"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
   </mergeCells>
-  <conditionalFormatting sqref="D9:D43">
+  <conditionalFormatting sqref="D9:D47">
     <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -3443,7 +3662,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:AB43">
+  <conditionalFormatting sqref="I6:AB47">
     <cfRule type="expression" dxfId="13" priority="1">
       <formula>AND(TODAY()&gt;=I$7, TODAY()&lt;J$7)</formula>
     </cfRule>
@@ -3456,7 +3675,7 @@
       <formula>AND(task_end&gt;=I$7,task_start&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I19:AB37">
+  <conditionalFormatting sqref="I19:AB41">
     <cfRule type="expression" dxfId="10" priority="4">
       <formula>AND(task_start&lt;=I$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$7)</formula>
     </cfRule>
@@ -3464,7 +3683,7 @@
       <formula>AND(task_end&gt;=I$7,task_start&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I39:AB43">
+  <conditionalFormatting sqref="I43:AB47">
     <cfRule type="expression" dxfId="8" priority="2">
       <formula>AND(task_start&lt;=I$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$7)</formula>
     </cfRule>
@@ -3472,7 +3691,7 @@
       <formula>AND(task_end&gt;=I$7,task_start&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC6:AC43">
+  <conditionalFormatting sqref="AC6:AC47">
     <cfRule type="expression" dxfId="6" priority="25">
       <formula>AND(TODAY()&gt;=AC$7, TODAY()&lt;#REF!)</formula>
     </cfRule>
@@ -3485,7 +3704,7 @@
       <formula>AND(task_end&gt;=AC$7,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC19:AC37">
+  <conditionalFormatting sqref="AC19:AC41">
     <cfRule type="expression" dxfId="3" priority="32">
       <formula>AND(task_start&lt;=AC$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=AC$7)</formula>
     </cfRule>
@@ -3493,7 +3712,7 @@
       <formula>AND(task_end&gt;=AC$7,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC39:AC43">
+  <conditionalFormatting sqref="AC43:AC47">
     <cfRule type="expression" dxfId="1" priority="36">
       <formula>AND(task_start&lt;=AC$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=AC$7)</formula>
     </cfRule>
@@ -3502,7 +3721,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C39:C43 C19:C37" xr:uid="{81BFDE51-3151-43F8-A7A1-718D27BBADDF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C43:C47 C19:C21 C22:C41" xr:uid="{81BFDE51-3151-43F8-A7A1-718D27BBADDF}">
       <formula1>$B$2:$B$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11:C17" xr:uid="{57E84E88-ADF7-4240-9B38-62294B230932}">
@@ -3532,7 +3751,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D9:D43</xm:sqref>
+          <xm:sqref>D9:D47</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3541,35 +3760,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3881,34 +4071,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09426A3-87E9-4865-8A6C-3456B026AE03}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3929,6 +4121,33 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>